--- a/2026/sixnationmatch.xlsx
+++ b/2026/sixnationmatch.xlsx
@@ -8,16 +8,18 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/williamgreenfield/Documents/dev/6n/2026/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{7DC8C294-A34E-FC49-B59D-FC48138D446B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0C96C131-AFEA-8A40-9B03-339B77E26B39}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="620" windowWidth="28040" windowHeight="16820" xr2:uid="{AD0B888C-2EE7-074B-B72D-275CD6FAB224}"/>
+    <workbookView xWindow="0" yWindow="620" windowWidth="28800" windowHeight="17380" activeTab="4" xr2:uid="{AD0B888C-2EE7-074B-B72D-275CD6FAB224}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
     <sheet name="Sheet3" sheetId="3" r:id="rId3"/>
+    <sheet name="Sheet4" sheetId="4" r:id="rId4"/>
+    <sheet name="Sheet5" sheetId="5" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="181029" calcOnSave="0" concurrentCalc="0"/>
+  <calcPr calcId="181029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
       <x15:workbookPr chartTrackingRefBase="1"/>
@@ -38,7 +40,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="777" uniqueCount="194">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1301" uniqueCount="216">
   <si>
     <t>France</t>
   </si>
@@ -620,6 +622,72 @@
   </si>
   <si>
     <t>P. Dimcheff</t>
+  </si>
+  <si>
+    <t>T. Farrell</t>
+  </si>
+  <si>
+    <t>N. Doak</t>
+  </si>
+  <si>
+    <t>T. Stewart</t>
+  </si>
+  <si>
+    <t>L. Hennessey</t>
+  </si>
+  <si>
+    <t>F. Douglas</t>
+  </si>
+  <si>
+    <t>D. Rae</t>
+  </si>
+  <si>
+    <t>R. Sutherland</t>
+  </si>
+  <si>
+    <t>D. Bamba</t>
+  </si>
+  <si>
+    <t>T. Allan</t>
+  </si>
+  <si>
+    <t>E. Daly</t>
+  </si>
+  <si>
+    <t>C. Murley</t>
+  </si>
+  <si>
+    <t>S. Atkinson</t>
+  </si>
+  <si>
+    <t>C. Cunningham-South</t>
+  </si>
+  <si>
+    <t>B. Aki</t>
+  </si>
+  <si>
+    <t>D. Murray</t>
+  </si>
+  <si>
+    <t>K. Rowe</t>
+  </si>
+  <si>
+    <t>M. Bradbury</t>
+  </si>
+  <si>
+    <t>A. Craig</t>
+  </si>
+  <si>
+    <t>S. Varney</t>
+  </si>
+  <si>
+    <t>T. Matiu</t>
+  </si>
+  <si>
+    <t>H. Auradou</t>
+  </si>
+  <si>
+    <t>J. Brennan</t>
   </si>
 </sst>
 </file>
@@ -11412,4 +11480,6991 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D41F4ECD-2A5A-974F-8360-B75D9B35868E}">
+  <dimension ref="A1:U158"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2">
+        <v>80</v>
+      </c>
+      <c r="G2">
+        <v>48</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>2</v>
+      </c>
+      <c r="N2">
+        <v>1</v>
+      </c>
+      <c r="U2">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>44</v>
+      </c>
+      <c r="B3">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>1</v>
+      </c>
+      <c r="G3">
+        <v>24</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>4</v>
+      </c>
+      <c r="U3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>45</v>
+      </c>
+      <c r="B4">
+        <v>70</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="D4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>39</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>5</v>
+      </c>
+      <c r="U4">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>194</v>
+      </c>
+      <c r="B5">
+        <v>10</v>
+      </c>
+      <c r="G5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>2</v>
+      </c>
+      <c r="U5">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6">
+        <v>80</v>
+      </c>
+      <c r="D6">
+        <v>1</v>
+      </c>
+      <c r="G6">
+        <v>48</v>
+      </c>
+      <c r="H6">
+        <v>3</v>
+      </c>
+      <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="N6">
+        <v>2</v>
+      </c>
+      <c r="U6">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7">
+        <v>70</v>
+      </c>
+      <c r="G7">
+        <v>20</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>7</v>
+      </c>
+      <c r="J7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8">
+        <v>80</v>
+      </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>2</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>27</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>13</v>
+      </c>
+      <c r="J8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9">
+        <v>10</v>
+      </c>
+      <c r="G9">
+        <v>20</v>
+      </c>
+      <c r="U9">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>195</v>
+      </c>
+      <c r="B10">
+        <v>13</v>
+      </c>
+      <c r="I10">
+        <v>1</v>
+      </c>
+      <c r="L10">
+        <v>1</v>
+      </c>
+      <c r="U10">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11">
+        <v>67</v>
+      </c>
+      <c r="D11">
+        <v>1</v>
+      </c>
+      <c r="G11">
+        <v>58</v>
+      </c>
+      <c r="H11">
+        <v>4</v>
+      </c>
+      <c r="I11">
+        <v>3</v>
+      </c>
+      <c r="L11">
+        <v>3</v>
+      </c>
+      <c r="U11">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12">
+        <v>80</v>
+      </c>
+      <c r="C12">
+        <v>1</v>
+      </c>
+      <c r="G12">
+        <v>37</v>
+      </c>
+      <c r="H12">
+        <v>3</v>
+      </c>
+      <c r="I12">
+        <v>14</v>
+      </c>
+      <c r="N12">
+        <v>3</v>
+      </c>
+      <c r="P12">
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <v>4</v>
+      </c>
+      <c r="U12">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13">
+        <v>80</v>
+      </c>
+      <c r="D13">
+        <v>1</v>
+      </c>
+      <c r="G13">
+        <v>23</v>
+      </c>
+      <c r="H13">
+        <v>1</v>
+      </c>
+      <c r="I13">
+        <v>18</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="N13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>4</v>
+      </c>
+      <c r="U13">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14">
+        <v>60</v>
+      </c>
+      <c r="G14">
+        <v>24</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>11</v>
+      </c>
+      <c r="R14">
+        <v>4</v>
+      </c>
+      <c r="U14">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15">
+        <v>20</v>
+      </c>
+      <c r="I15">
+        <v>8</v>
+      </c>
+      <c r="N15">
+        <v>1</v>
+      </c>
+      <c r="U15">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16">
+        <v>80</v>
+      </c>
+      <c r="G16">
+        <v>9</v>
+      </c>
+      <c r="I16">
+        <v>13</v>
+      </c>
+      <c r="J16">
+        <v>1</v>
+      </c>
+      <c r="N16">
+        <v>2</v>
+      </c>
+      <c r="O16">
+        <v>1</v>
+      </c>
+      <c r="P16">
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <v>4</v>
+      </c>
+      <c r="U16">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17">
+        <v>20</v>
+      </c>
+      <c r="G17">
+        <v>15</v>
+      </c>
+      <c r="I17">
+        <v>7</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="U17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>59</v>
+      </c>
+      <c r="B18">
+        <v>60</v>
+      </c>
+      <c r="G18">
+        <v>13</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>5</v>
+      </c>
+      <c r="J18">
+        <v>2</v>
+      </c>
+      <c r="R18">
+        <v>4</v>
+      </c>
+      <c r="U18">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>61</v>
+      </c>
+      <c r="B19">
+        <v>20</v>
+      </c>
+      <c r="I19">
+        <v>3</v>
+      </c>
+      <c r="U19">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20">
+        <v>60</v>
+      </c>
+      <c r="G20">
+        <v>14</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>5</v>
+      </c>
+      <c r="J20">
+        <v>1</v>
+      </c>
+      <c r="N20">
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <v>4</v>
+      </c>
+      <c r="U20">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21">
+        <v>17</v>
+      </c>
+      <c r="G21">
+        <v>1</v>
+      </c>
+      <c r="I21">
+        <v>6</v>
+      </c>
+      <c r="U21">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22">
+        <v>63</v>
+      </c>
+      <c r="I22">
+        <v>10</v>
+      </c>
+      <c r="R22">
+        <v>4</v>
+      </c>
+      <c r="U22">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23">
+        <v>63</v>
+      </c>
+      <c r="G23">
+        <v>30</v>
+      </c>
+      <c r="H23">
+        <v>2</v>
+      </c>
+      <c r="I23">
+        <v>17</v>
+      </c>
+      <c r="N23">
+        <v>1</v>
+      </c>
+      <c r="P23">
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <v>4</v>
+      </c>
+      <c r="U23">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>196</v>
+      </c>
+      <c r="B24">
+        <v>17</v>
+      </c>
+      <c r="G24">
+        <v>3</v>
+      </c>
+      <c r="I24">
+        <v>3</v>
+      </c>
+      <c r="U24">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A26" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2</v>
+      </c>
+      <c r="D26" t="s">
+        <v>3</v>
+      </c>
+      <c r="E26" t="s">
+        <v>4</v>
+      </c>
+      <c r="F26" t="s">
+        <v>5</v>
+      </c>
+      <c r="G26" t="s">
+        <v>6</v>
+      </c>
+      <c r="H26" t="s">
+        <v>7</v>
+      </c>
+      <c r="I26" t="s">
+        <v>8</v>
+      </c>
+      <c r="J26" t="s">
+        <v>9</v>
+      </c>
+      <c r="K26" t="s">
+        <v>10</v>
+      </c>
+      <c r="L26" t="s">
+        <v>11</v>
+      </c>
+      <c r="M26" t="s">
+        <v>12</v>
+      </c>
+      <c r="N26" t="s">
+        <v>13</v>
+      </c>
+      <c r="O26" t="s">
+        <v>14</v>
+      </c>
+      <c r="P26" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>16</v>
+      </c>
+      <c r="R26" t="s">
+        <v>17</v>
+      </c>
+      <c r="S26" t="s">
+        <v>18</v>
+      </c>
+      <c r="T26" t="s">
+        <v>19</v>
+      </c>
+      <c r="U26" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A27" t="s">
+        <v>136</v>
+      </c>
+      <c r="B27">
+        <v>80</v>
+      </c>
+      <c r="G27">
+        <v>14</v>
+      </c>
+      <c r="I27">
+        <v>6</v>
+      </c>
+      <c r="U27">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>137</v>
+      </c>
+      <c r="B28">
+        <v>69</v>
+      </c>
+      <c r="G28">
+        <v>5</v>
+      </c>
+      <c r="I28">
+        <v>5</v>
+      </c>
+      <c r="U28">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>138</v>
+      </c>
+      <c r="B29">
+        <v>80</v>
+      </c>
+      <c r="G29">
+        <v>28</v>
+      </c>
+      <c r="H29">
+        <v>2</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
+      </c>
+      <c r="K29">
+        <v>1</v>
+      </c>
+      <c r="L29">
+        <v>1</v>
+      </c>
+      <c r="U29">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>168</v>
+      </c>
+      <c r="B30">
+        <v>80</v>
+      </c>
+      <c r="G30">
+        <v>18</v>
+      </c>
+      <c r="I30">
+        <v>14</v>
+      </c>
+      <c r="U30">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>197</v>
+      </c>
+      <c r="B31">
+        <v>11</v>
+      </c>
+      <c r="U31">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>140</v>
+      </c>
+      <c r="B32">
+        <v>80</v>
+      </c>
+      <c r="G32">
+        <v>13</v>
+      </c>
+      <c r="H32">
+        <v>3</v>
+      </c>
+      <c r="I32">
+        <v>14</v>
+      </c>
+      <c r="J32">
+        <v>1</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="U32">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>142</v>
+      </c>
+      <c r="B33">
+        <v>80</v>
+      </c>
+      <c r="E33">
+        <v>2</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="H33">
+        <v>2</v>
+      </c>
+      <c r="I33">
+        <v>4</v>
+      </c>
+      <c r="L33">
+        <v>1</v>
+      </c>
+      <c r="U33">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>144</v>
+      </c>
+      <c r="B34">
+        <v>71</v>
+      </c>
+      <c r="D34">
+        <v>1</v>
+      </c>
+      <c r="G34">
+        <v>3</v>
+      </c>
+      <c r="I34">
+        <v>8</v>
+      </c>
+      <c r="L34">
+        <v>1</v>
+      </c>
+      <c r="S34">
+        <v>1</v>
+      </c>
+      <c r="U34">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>182</v>
+      </c>
+      <c r="B35">
+        <v>80</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="G35">
+        <v>7</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>26</v>
+      </c>
+      <c r="J35">
+        <v>1</v>
+      </c>
+      <c r="P35">
+        <v>1</v>
+      </c>
+      <c r="R35">
+        <v>6</v>
+      </c>
+      <c r="U35">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>170</v>
+      </c>
+      <c r="B36">
+        <v>35</v>
+      </c>
+      <c r="G36">
+        <v>15</v>
+      </c>
+      <c r="I36">
+        <v>4</v>
+      </c>
+      <c r="R36">
+        <v>4</v>
+      </c>
+      <c r="U36">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>147</v>
+      </c>
+      <c r="B37">
+        <v>80</v>
+      </c>
+      <c r="G37">
+        <v>9</v>
+      </c>
+      <c r="I37">
+        <v>33</v>
+      </c>
+      <c r="J37">
+        <v>1</v>
+      </c>
+      <c r="P37">
+        <v>1</v>
+      </c>
+      <c r="R37">
+        <v>6</v>
+      </c>
+      <c r="U37">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>148</v>
+      </c>
+      <c r="B38">
+        <v>45</v>
+      </c>
+      <c r="G38">
+        <v>31</v>
+      </c>
+      <c r="H38">
+        <v>1</v>
+      </c>
+      <c r="I38">
+        <v>16</v>
+      </c>
+      <c r="R38">
+        <v>2</v>
+      </c>
+      <c r="U38">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>149</v>
+      </c>
+      <c r="B39">
+        <v>24</v>
+      </c>
+      <c r="G39">
+        <v>2</v>
+      </c>
+      <c r="I39">
+        <v>1</v>
+      </c>
+      <c r="R39">
+        <v>4</v>
+      </c>
+      <c r="U39">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>150</v>
+      </c>
+      <c r="B40">
+        <v>56</v>
+      </c>
+      <c r="G40">
+        <v>3</v>
+      </c>
+      <c r="I40">
+        <v>20</v>
+      </c>
+      <c r="N40">
+        <v>1</v>
+      </c>
+      <c r="R40">
+        <v>2</v>
+      </c>
+      <c r="U40">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>151</v>
+      </c>
+      <c r="B41">
+        <v>80</v>
+      </c>
+      <c r="G41">
+        <v>7</v>
+      </c>
+      <c r="I41">
+        <v>27</v>
+      </c>
+      <c r="J41">
+        <v>1</v>
+      </c>
+      <c r="R41">
+        <v>6</v>
+      </c>
+      <c r="U41">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>152</v>
+      </c>
+      <c r="B42">
+        <v>45</v>
+      </c>
+      <c r="C42">
+        <v>1</v>
+      </c>
+      <c r="G42">
+        <v>38</v>
+      </c>
+      <c r="H42">
+        <v>2</v>
+      </c>
+      <c r="I42">
+        <v>13</v>
+      </c>
+      <c r="R42">
+        <v>2</v>
+      </c>
+      <c r="U42">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>153</v>
+      </c>
+      <c r="B43">
+        <v>56</v>
+      </c>
+      <c r="I43">
+        <v>14</v>
+      </c>
+      <c r="J43">
+        <v>2</v>
+      </c>
+      <c r="N43">
+        <v>1</v>
+      </c>
+      <c r="R43">
+        <v>2</v>
+      </c>
+      <c r="U43">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>154</v>
+      </c>
+      <c r="B44">
+        <v>24</v>
+      </c>
+      <c r="G44">
+        <v>2</v>
+      </c>
+      <c r="I44">
+        <v>2</v>
+      </c>
+      <c r="R44">
+        <v>4</v>
+      </c>
+      <c r="U44">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>155</v>
+      </c>
+      <c r="B45">
+        <v>35</v>
+      </c>
+      <c r="I45">
+        <v>3</v>
+      </c>
+      <c r="R45">
+        <v>4</v>
+      </c>
+      <c r="U45">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>171</v>
+      </c>
+      <c r="B46">
+        <v>24</v>
+      </c>
+      <c r="G46">
+        <v>5</v>
+      </c>
+      <c r="I46">
+        <v>3</v>
+      </c>
+      <c r="R46">
+        <v>4</v>
+      </c>
+      <c r="U46">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>157</v>
+      </c>
+      <c r="B47">
+        <v>56</v>
+      </c>
+      <c r="G47">
+        <v>13</v>
+      </c>
+      <c r="I47">
+        <v>25</v>
+      </c>
+      <c r="J47">
+        <v>1</v>
+      </c>
+      <c r="P47">
+        <v>1</v>
+      </c>
+      <c r="R47">
+        <v>2</v>
+      </c>
+      <c r="U47">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A55" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1</v>
+      </c>
+      <c r="C55" t="s">
+        <v>2</v>
+      </c>
+      <c r="D55" t="s">
+        <v>3</v>
+      </c>
+      <c r="E55" t="s">
+        <v>4</v>
+      </c>
+      <c r="F55" t="s">
+        <v>5</v>
+      </c>
+      <c r="G55" t="s">
+        <v>6</v>
+      </c>
+      <c r="H55" t="s">
+        <v>7</v>
+      </c>
+      <c r="I55" t="s">
+        <v>8</v>
+      </c>
+      <c r="J55" t="s">
+        <v>9</v>
+      </c>
+      <c r="K55" t="s">
+        <v>10</v>
+      </c>
+      <c r="L55" t="s">
+        <v>11</v>
+      </c>
+      <c r="M55" t="s">
+        <v>12</v>
+      </c>
+      <c r="N55" t="s">
+        <v>13</v>
+      </c>
+      <c r="O55" t="s">
+        <v>14</v>
+      </c>
+      <c r="P55" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>16</v>
+      </c>
+      <c r="R55" t="s">
+        <v>17</v>
+      </c>
+      <c r="S55" t="s">
+        <v>18</v>
+      </c>
+      <c r="T55" t="s">
+        <v>19</v>
+      </c>
+      <c r="U55" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A56" t="s">
+        <v>90</v>
+      </c>
+      <c r="B56">
+        <v>80</v>
+      </c>
+      <c r="C56">
+        <v>2</v>
+      </c>
+      <c r="G56">
+        <v>50</v>
+      </c>
+      <c r="H56">
+        <v>8</v>
+      </c>
+      <c r="I56">
+        <v>4</v>
+      </c>
+      <c r="N56">
+        <v>1</v>
+      </c>
+      <c r="U56">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A57" t="s">
+        <v>184</v>
+      </c>
+      <c r="B57">
+        <v>80</v>
+      </c>
+      <c r="D57">
+        <v>1</v>
+      </c>
+      <c r="G57">
+        <v>73</v>
+      </c>
+      <c r="H57">
+        <v>5</v>
+      </c>
+      <c r="I57">
+        <v>2</v>
+      </c>
+      <c r="N57">
+        <v>3</v>
+      </c>
+      <c r="U57">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A58" t="s">
+        <v>91</v>
+      </c>
+      <c r="B58">
+        <v>67</v>
+      </c>
+      <c r="C58">
+        <v>2</v>
+      </c>
+      <c r="G58">
+        <v>117</v>
+      </c>
+      <c r="H58">
+        <v>4</v>
+      </c>
+      <c r="I58">
+        <v>5</v>
+      </c>
+      <c r="N58">
+        <v>1</v>
+      </c>
+      <c r="Q58">
+        <v>1</v>
+      </c>
+      <c r="U58">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>92</v>
+      </c>
+      <c r="B59">
+        <v>56</v>
+      </c>
+      <c r="G59">
+        <v>27</v>
+      </c>
+      <c r="H59">
+        <v>3</v>
+      </c>
+      <c r="I59">
+        <v>5</v>
+      </c>
+      <c r="N59">
+        <v>1</v>
+      </c>
+      <c r="U59">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>93</v>
+      </c>
+      <c r="B60">
+        <v>24</v>
+      </c>
+      <c r="C60">
+        <v>1</v>
+      </c>
+      <c r="G60">
+        <v>33</v>
+      </c>
+      <c r="H60">
+        <v>2</v>
+      </c>
+      <c r="I60">
+        <v>2</v>
+      </c>
+      <c r="U60">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>94</v>
+      </c>
+      <c r="B61">
+        <v>80</v>
+      </c>
+      <c r="D61">
+        <v>1</v>
+      </c>
+      <c r="G61">
+        <v>32</v>
+      </c>
+      <c r="H61">
+        <v>4</v>
+      </c>
+      <c r="I61">
+        <v>8</v>
+      </c>
+      <c r="U61">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>95</v>
+      </c>
+      <c r="B62">
+        <v>80</v>
+      </c>
+      <c r="D62">
+        <v>1</v>
+      </c>
+      <c r="E62">
+        <v>6</v>
+      </c>
+      <c r="F62">
+        <v>1</v>
+      </c>
+      <c r="G62">
+        <v>17</v>
+      </c>
+      <c r="I62">
+        <v>3</v>
+      </c>
+      <c r="L62">
+        <v>1</v>
+      </c>
+      <c r="N62">
+        <v>1</v>
+      </c>
+      <c r="U62">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>96</v>
+      </c>
+      <c r="B63">
+        <v>16</v>
+      </c>
+      <c r="G63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>4</v>
+      </c>
+      <c r="L63">
+        <v>1</v>
+      </c>
+      <c r="U63">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>97</v>
+      </c>
+      <c r="B64">
+        <v>64</v>
+      </c>
+      <c r="C64">
+        <v>1</v>
+      </c>
+      <c r="G64">
+        <v>12</v>
+      </c>
+      <c r="H64">
+        <v>1</v>
+      </c>
+      <c r="I64">
+        <v>4</v>
+      </c>
+      <c r="L64">
+        <v>2</v>
+      </c>
+      <c r="U64">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>186</v>
+      </c>
+      <c r="B65">
+        <v>26</v>
+      </c>
+      <c r="I65">
+        <v>6</v>
+      </c>
+      <c r="J65">
+        <v>1</v>
+      </c>
+      <c r="R65">
+        <v>1</v>
+      </c>
+      <c r="S65">
+        <v>1</v>
+      </c>
+      <c r="U65">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>98</v>
+      </c>
+      <c r="B66">
+        <v>80</v>
+      </c>
+      <c r="G66">
+        <v>10</v>
+      </c>
+      <c r="I66">
+        <v>15</v>
+      </c>
+      <c r="N66">
+        <v>1</v>
+      </c>
+      <c r="R66">
+        <v>5</v>
+      </c>
+      <c r="U66">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>99</v>
+      </c>
+      <c r="B67">
+        <v>80</v>
+      </c>
+      <c r="G67">
+        <v>42</v>
+      </c>
+      <c r="H67">
+        <v>3</v>
+      </c>
+      <c r="I67">
+        <v>7</v>
+      </c>
+      <c r="J67">
+        <v>1</v>
+      </c>
+      <c r="N67">
+        <v>1</v>
+      </c>
+      <c r="R67">
+        <v>5</v>
+      </c>
+      <c r="U67">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>198</v>
+      </c>
+      <c r="B68">
+        <v>13</v>
+      </c>
+      <c r="I68">
+        <v>6</v>
+      </c>
+      <c r="U68">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>100</v>
+      </c>
+      <c r="B69">
+        <v>80</v>
+      </c>
+      <c r="G69">
+        <v>15</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69">
+        <v>8</v>
+      </c>
+      <c r="R69">
+        <v>5</v>
+      </c>
+      <c r="U69">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>101</v>
+      </c>
+      <c r="B70">
+        <v>34</v>
+      </c>
+      <c r="G70">
+        <v>1</v>
+      </c>
+      <c r="I70">
+        <v>6</v>
+      </c>
+      <c r="R70">
+        <v>3</v>
+      </c>
+      <c r="U70">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>102</v>
+      </c>
+      <c r="B71">
+        <v>52</v>
+      </c>
+      <c r="G71">
+        <v>1</v>
+      </c>
+      <c r="I71">
+        <v>5</v>
+      </c>
+      <c r="O71">
+        <v>1</v>
+      </c>
+      <c r="R71">
+        <v>4</v>
+      </c>
+      <c r="U71">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>103</v>
+      </c>
+      <c r="B72">
+        <v>46</v>
+      </c>
+      <c r="G72">
+        <v>3</v>
+      </c>
+      <c r="I72">
+        <v>7</v>
+      </c>
+      <c r="R72">
+        <v>2</v>
+      </c>
+      <c r="U72">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>105</v>
+      </c>
+      <c r="B73">
+        <v>41</v>
+      </c>
+      <c r="G73">
+        <v>8</v>
+      </c>
+      <c r="H73">
+        <v>1</v>
+      </c>
+      <c r="I73">
+        <v>6</v>
+      </c>
+      <c r="R73">
+        <v>1</v>
+      </c>
+      <c r="U73">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>199</v>
+      </c>
+      <c r="B74">
+        <v>39</v>
+      </c>
+      <c r="I74">
+        <v>2</v>
+      </c>
+      <c r="J74">
+        <v>1</v>
+      </c>
+      <c r="R74">
+        <v>4</v>
+      </c>
+      <c r="U74">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>108</v>
+      </c>
+      <c r="B75">
+        <v>64</v>
+      </c>
+      <c r="C75">
+        <v>1</v>
+      </c>
+      <c r="G75">
+        <v>6</v>
+      </c>
+      <c r="H75">
+        <v>1</v>
+      </c>
+      <c r="I75">
+        <v>3</v>
+      </c>
+      <c r="J75">
+        <v>1</v>
+      </c>
+      <c r="R75">
+        <v>5</v>
+      </c>
+      <c r="U75">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>200</v>
+      </c>
+      <c r="B76">
+        <v>16</v>
+      </c>
+      <c r="G76">
+        <v>1</v>
+      </c>
+      <c r="I76">
+        <v>5</v>
+      </c>
+      <c r="U76">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>109</v>
+      </c>
+      <c r="B77">
+        <v>28</v>
+      </c>
+      <c r="G77">
+        <v>7</v>
+      </c>
+      <c r="I77">
+        <v>6</v>
+      </c>
+      <c r="N77">
+        <v>1</v>
+      </c>
+      <c r="R77">
+        <v>1</v>
+      </c>
+      <c r="U77">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>110</v>
+      </c>
+      <c r="B78">
+        <v>52</v>
+      </c>
+      <c r="D78">
+        <v>1</v>
+      </c>
+      <c r="G78">
+        <v>15</v>
+      </c>
+      <c r="I78">
+        <v>3</v>
+      </c>
+      <c r="R78">
+        <v>4</v>
+      </c>
+      <c r="U78">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A80" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B80" t="s">
+        <v>1</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2</v>
+      </c>
+      <c r="D80" t="s">
+        <v>3</v>
+      </c>
+      <c r="E80" t="s">
+        <v>4</v>
+      </c>
+      <c r="F80" t="s">
+        <v>5</v>
+      </c>
+      <c r="G80" t="s">
+        <v>6</v>
+      </c>
+      <c r="H80" t="s">
+        <v>7</v>
+      </c>
+      <c r="I80" t="s">
+        <v>8</v>
+      </c>
+      <c r="J80" t="s">
+        <v>9</v>
+      </c>
+      <c r="K80" t="s">
+        <v>10</v>
+      </c>
+      <c r="L80" t="s">
+        <v>11</v>
+      </c>
+      <c r="M80" t="s">
+        <v>12</v>
+      </c>
+      <c r="N80" t="s">
+        <v>13</v>
+      </c>
+      <c r="O80" t="s">
+        <v>14</v>
+      </c>
+      <c r="P80" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>16</v>
+      </c>
+      <c r="R80" t="s">
+        <v>17</v>
+      </c>
+      <c r="S80" t="s">
+        <v>18</v>
+      </c>
+      <c r="T80" t="s">
+        <v>19</v>
+      </c>
+      <c r="U80" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>21</v>
+      </c>
+      <c r="B81">
+        <v>80</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="D81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>63</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
+        <v>4</v>
+      </c>
+      <c r="J81">
+        <v>1</v>
+      </c>
+      <c r="U81">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A82" t="s">
+        <v>22</v>
+      </c>
+      <c r="B82">
+        <v>80</v>
+      </c>
+      <c r="C82">
+        <v>1</v>
+      </c>
+      <c r="D82">
+        <v>3</v>
+      </c>
+      <c r="G82">
+        <v>96</v>
+      </c>
+      <c r="H82">
+        <v>2</v>
+      </c>
+      <c r="I82">
+        <v>10</v>
+      </c>
+      <c r="L82">
+        <v>2</v>
+      </c>
+      <c r="U82">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A83" t="s">
+        <v>23</v>
+      </c>
+      <c r="B83">
+        <v>80</v>
+      </c>
+      <c r="C83">
+        <v>2</v>
+      </c>
+      <c r="E83">
+        <v>5</v>
+      </c>
+      <c r="G83">
+        <v>83</v>
+      </c>
+      <c r="H83">
+        <v>3</v>
+      </c>
+      <c r="I83">
+        <v>2</v>
+      </c>
+      <c r="J83">
+        <v>1</v>
+      </c>
+      <c r="U83">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A84" t="s">
+        <v>189</v>
+      </c>
+      <c r="B84">
+        <v>36</v>
+      </c>
+      <c r="G84">
+        <v>22</v>
+      </c>
+      <c r="H84">
+        <v>2</v>
+      </c>
+      <c r="I84">
+        <v>6</v>
+      </c>
+      <c r="U84">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>24</v>
+      </c>
+      <c r="B85">
+        <v>44</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="I85">
+        <v>8</v>
+      </c>
+      <c r="U85">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>26</v>
+      </c>
+      <c r="B86">
+        <v>80</v>
+      </c>
+      <c r="G86">
+        <v>34</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>8</v>
+      </c>
+      <c r="J86">
+        <v>1</v>
+      </c>
+      <c r="N86">
+        <v>1</v>
+      </c>
+      <c r="U86">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>27</v>
+      </c>
+      <c r="B87">
+        <v>70</v>
+      </c>
+      <c r="D87">
+        <v>1</v>
+      </c>
+      <c r="G87">
+        <v>54</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>6</v>
+      </c>
+      <c r="N87">
+        <v>1</v>
+      </c>
+      <c r="S87">
+        <v>1</v>
+      </c>
+      <c r="U87">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>28</v>
+      </c>
+      <c r="B88">
+        <v>69</v>
+      </c>
+      <c r="C88">
+        <v>1</v>
+      </c>
+      <c r="G88">
+        <v>38</v>
+      </c>
+      <c r="H88">
+        <v>2</v>
+      </c>
+      <c r="I88">
+        <v>4</v>
+      </c>
+      <c r="U88">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>29</v>
+      </c>
+      <c r="B89">
+        <v>11</v>
+      </c>
+      <c r="D89">
+        <v>1</v>
+      </c>
+      <c r="G89">
+        <v>16</v>
+      </c>
+      <c r="H89">
+        <v>1</v>
+      </c>
+      <c r="U89">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>30</v>
+      </c>
+      <c r="B90">
+        <v>80</v>
+      </c>
+      <c r="G90">
+        <v>3</v>
+      </c>
+      <c r="I90">
+        <v>18</v>
+      </c>
+      <c r="J90">
+        <v>1</v>
+      </c>
+      <c r="R90">
+        <v>3</v>
+      </c>
+      <c r="U90">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>31</v>
+      </c>
+      <c r="B91">
+        <v>80</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>22</v>
+      </c>
+      <c r="I91">
+        <v>28</v>
+      </c>
+      <c r="J91">
+        <v>1</v>
+      </c>
+      <c r="R91">
+        <v>3</v>
+      </c>
+      <c r="U91">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>32</v>
+      </c>
+      <c r="B92">
+        <v>42</v>
+      </c>
+      <c r="G92">
+        <v>19</v>
+      </c>
+      <c r="H92">
+        <v>1</v>
+      </c>
+      <c r="I92">
+        <v>16</v>
+      </c>
+      <c r="R92">
+        <v>2</v>
+      </c>
+      <c r="U92">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>33</v>
+      </c>
+      <c r="B93">
+        <v>27</v>
+      </c>
+      <c r="G93">
+        <v>4</v>
+      </c>
+      <c r="H93">
+        <v>1</v>
+      </c>
+      <c r="I93">
+        <v>10</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="N93">
+        <v>1</v>
+      </c>
+      <c r="R93">
+        <v>1</v>
+      </c>
+      <c r="S93">
+        <v>1</v>
+      </c>
+      <c r="U93">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>34</v>
+      </c>
+      <c r="B94">
+        <v>44</v>
+      </c>
+      <c r="G94">
+        <v>6</v>
+      </c>
+      <c r="I94">
+        <v>10</v>
+      </c>
+      <c r="R94">
+        <v>2</v>
+      </c>
+      <c r="U94">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>174</v>
+      </c>
+      <c r="B95">
+        <v>36</v>
+      </c>
+      <c r="G95">
+        <v>10</v>
+      </c>
+      <c r="I95">
+        <v>6</v>
+      </c>
+      <c r="N95">
+        <v>1</v>
+      </c>
+      <c r="O95">
+        <v>1</v>
+      </c>
+      <c r="R95">
+        <v>1</v>
+      </c>
+      <c r="U95">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>35</v>
+      </c>
+      <c r="B96">
+        <v>44</v>
+      </c>
+      <c r="G96">
+        <v>11</v>
+      </c>
+      <c r="I96">
+        <v>11</v>
+      </c>
+      <c r="R96">
+        <v>2</v>
+      </c>
+      <c r="U96">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>36</v>
+      </c>
+      <c r="B97">
+        <v>36</v>
+      </c>
+      <c r="G97">
+        <v>22</v>
+      </c>
+      <c r="H97">
+        <v>2</v>
+      </c>
+      <c r="I97">
+        <v>8</v>
+      </c>
+      <c r="J97">
+        <v>1</v>
+      </c>
+      <c r="N97">
+        <v>2</v>
+      </c>
+      <c r="R97">
+        <v>1</v>
+      </c>
+      <c r="U97">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>37</v>
+      </c>
+      <c r="B98">
+        <v>52</v>
+      </c>
+      <c r="I98">
+        <v>7</v>
+      </c>
+      <c r="J98">
+        <v>1</v>
+      </c>
+      <c r="R98">
+        <v>2</v>
+      </c>
+      <c r="U98">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>201</v>
+      </c>
+      <c r="B99">
+        <v>28</v>
+      </c>
+      <c r="G99">
+        <v>7</v>
+      </c>
+      <c r="H99">
+        <v>1</v>
+      </c>
+      <c r="I99">
+        <v>3</v>
+      </c>
+      <c r="R99">
+        <v>1</v>
+      </c>
+      <c r="U99">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>38</v>
+      </c>
+      <c r="B100">
+        <v>52</v>
+      </c>
+      <c r="G100">
+        <v>2</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>22</v>
+      </c>
+      <c r="J100">
+        <v>1</v>
+      </c>
+      <c r="R100">
+        <v>2</v>
+      </c>
+      <c r="U100">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>39</v>
+      </c>
+      <c r="B101">
+        <v>28</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="I101">
+        <v>6</v>
+      </c>
+      <c r="R101">
+        <v>1</v>
+      </c>
+      <c r="U101">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>40</v>
+      </c>
+      <c r="B102">
+        <v>44</v>
+      </c>
+      <c r="G102">
+        <v>2</v>
+      </c>
+      <c r="I102">
+        <v>11</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="R102">
+        <v>2</v>
+      </c>
+      <c r="U102">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>41</v>
+      </c>
+      <c r="B103">
+        <v>36</v>
+      </c>
+      <c r="I103">
+        <v>4</v>
+      </c>
+      <c r="R103">
+        <v>1</v>
+      </c>
+      <c r="U103">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="110" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A110" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B110" t="s">
+        <v>1</v>
+      </c>
+      <c r="C110" t="s">
+        <v>2</v>
+      </c>
+      <c r="D110" t="s">
+        <v>3</v>
+      </c>
+      <c r="E110" t="s">
+        <v>4</v>
+      </c>
+      <c r="F110" t="s">
+        <v>5</v>
+      </c>
+      <c r="G110" t="s">
+        <v>6</v>
+      </c>
+      <c r="H110" t="s">
+        <v>7</v>
+      </c>
+      <c r="I110" t="s">
+        <v>8</v>
+      </c>
+      <c r="J110" t="s">
+        <v>9</v>
+      </c>
+      <c r="K110" t="s">
+        <v>10</v>
+      </c>
+      <c r="L110" t="s">
+        <v>11</v>
+      </c>
+      <c r="M110" t="s">
+        <v>12</v>
+      </c>
+      <c r="N110" t="s">
+        <v>13</v>
+      </c>
+      <c r="O110" t="s">
+        <v>14</v>
+      </c>
+      <c r="P110" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q110" t="s">
+        <v>16</v>
+      </c>
+      <c r="R110" t="s">
+        <v>17</v>
+      </c>
+      <c r="S110" t="s">
+        <v>18</v>
+      </c>
+      <c r="T110" t="s">
+        <v>19</v>
+      </c>
+      <c r="U110" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="111" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A111" t="s">
+        <v>67</v>
+      </c>
+      <c r="B111">
+        <v>80</v>
+      </c>
+      <c r="G111">
+        <v>50</v>
+      </c>
+      <c r="H111">
+        <v>1</v>
+      </c>
+      <c r="I111">
+        <v>6</v>
+      </c>
+      <c r="N111">
+        <v>5</v>
+      </c>
+      <c r="U111">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="112" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A112" t="s">
+        <v>68</v>
+      </c>
+      <c r="B112">
+        <v>80</v>
+      </c>
+      <c r="G112">
+        <v>20</v>
+      </c>
+      <c r="I112">
+        <v>7</v>
+      </c>
+      <c r="N112">
+        <v>2</v>
+      </c>
+      <c r="P112">
+        <v>1</v>
+      </c>
+      <c r="U112">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A113" t="s">
+        <v>69</v>
+      </c>
+      <c r="B113">
+        <v>73</v>
+      </c>
+      <c r="G113">
+        <v>38</v>
+      </c>
+      <c r="H113">
+        <v>2</v>
+      </c>
+      <c r="I113">
+        <v>2</v>
+      </c>
+      <c r="J113">
+        <v>1</v>
+      </c>
+      <c r="N113">
+        <v>1</v>
+      </c>
+      <c r="U113">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>70</v>
+      </c>
+      <c r="B114">
+        <v>51</v>
+      </c>
+      <c r="G114">
+        <v>5</v>
+      </c>
+      <c r="I114">
+        <v>3</v>
+      </c>
+      <c r="L114">
+        <v>1</v>
+      </c>
+      <c r="U114">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>71</v>
+      </c>
+      <c r="B115">
+        <v>80</v>
+      </c>
+      <c r="C115">
+        <v>1</v>
+      </c>
+      <c r="D115">
+        <v>1</v>
+      </c>
+      <c r="G115">
+        <v>87</v>
+      </c>
+      <c r="H115">
+        <v>5</v>
+      </c>
+      <c r="I115">
+        <v>7</v>
+      </c>
+      <c r="Q115">
+        <v>1</v>
+      </c>
+      <c r="U115">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>202</v>
+      </c>
+      <c r="B116">
+        <v>7</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="H116">
+        <v>1</v>
+      </c>
+      <c r="U116">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>72</v>
+      </c>
+      <c r="B117">
+        <v>80</v>
+      </c>
+      <c r="E117">
+        <v>2</v>
+      </c>
+      <c r="F117">
+        <v>3</v>
+      </c>
+      <c r="I117">
+        <v>8</v>
+      </c>
+      <c r="L117">
+        <v>2</v>
+      </c>
+      <c r="P117">
+        <v>1</v>
+      </c>
+      <c r="U117">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>73</v>
+      </c>
+      <c r="B118">
+        <v>29</v>
+      </c>
+      <c r="C118">
+        <v>1</v>
+      </c>
+      <c r="G118">
+        <v>18</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
+        <v>1</v>
+      </c>
+      <c r="U118">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>74</v>
+      </c>
+      <c r="B119">
+        <v>29</v>
+      </c>
+      <c r="G119">
+        <v>6</v>
+      </c>
+      <c r="H119">
+        <v>1</v>
+      </c>
+      <c r="I119">
+        <v>1</v>
+      </c>
+      <c r="L119">
+        <v>3</v>
+      </c>
+      <c r="U119">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>75</v>
+      </c>
+      <c r="B120">
+        <v>51</v>
+      </c>
+      <c r="D120">
+        <v>1</v>
+      </c>
+      <c r="G120">
+        <v>2</v>
+      </c>
+      <c r="I120">
+        <v>6</v>
+      </c>
+      <c r="L120">
+        <v>1</v>
+      </c>
+      <c r="U120">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>76</v>
+      </c>
+      <c r="B121">
+        <v>80</v>
+      </c>
+      <c r="G121">
+        <v>44</v>
+      </c>
+      <c r="H121">
+        <v>7</v>
+      </c>
+      <c r="I121">
+        <v>13</v>
+      </c>
+      <c r="R121">
+        <v>1</v>
+      </c>
+      <c r="U121">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>77</v>
+      </c>
+      <c r="B122">
+        <v>80</v>
+      </c>
+      <c r="G122">
+        <v>3</v>
+      </c>
+      <c r="I122">
+        <v>10</v>
+      </c>
+      <c r="P122">
+        <v>1</v>
+      </c>
+      <c r="R122">
+        <v>1</v>
+      </c>
+      <c r="U122">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>78</v>
+      </c>
+      <c r="B123">
+        <v>73</v>
+      </c>
+      <c r="G123">
+        <v>6</v>
+      </c>
+      <c r="H123">
+        <v>2</v>
+      </c>
+      <c r="I123">
+        <v>15</v>
+      </c>
+      <c r="N123">
+        <v>1</v>
+      </c>
+      <c r="R123">
+        <v>1</v>
+      </c>
+      <c r="U123">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>79</v>
+      </c>
+      <c r="B124">
+        <v>80</v>
+      </c>
+      <c r="G124">
+        <v>1</v>
+      </c>
+      <c r="H124">
+        <v>1</v>
+      </c>
+      <c r="I124">
+        <v>9</v>
+      </c>
+      <c r="J124">
+        <v>2</v>
+      </c>
+      <c r="R124">
+        <v>1</v>
+      </c>
+      <c r="U124">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>80</v>
+      </c>
+      <c r="B125">
+        <v>7</v>
+      </c>
+      <c r="I125">
+        <v>1</v>
+      </c>
+      <c r="U125">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>81</v>
+      </c>
+      <c r="B126">
+        <v>31</v>
+      </c>
+      <c r="G126">
+        <v>15</v>
+      </c>
+      <c r="I126">
+        <v>6</v>
+      </c>
+      <c r="U126">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>82</v>
+      </c>
+      <c r="B127">
+        <v>49</v>
+      </c>
+      <c r="G127">
+        <v>8</v>
+      </c>
+      <c r="I127">
+        <v>8</v>
+      </c>
+      <c r="R127">
+        <v>1</v>
+      </c>
+      <c r="U127">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>83</v>
+      </c>
+      <c r="B128">
+        <v>51</v>
+      </c>
+      <c r="I128">
+        <v>9</v>
+      </c>
+      <c r="J128">
+        <v>2</v>
+      </c>
+      <c r="R128">
+        <v>1</v>
+      </c>
+      <c r="U128">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>84</v>
+      </c>
+      <c r="B129">
+        <v>58</v>
+      </c>
+      <c r="G129">
+        <v>9</v>
+      </c>
+      <c r="I129">
+        <v>9</v>
+      </c>
+      <c r="P129">
+        <v>1</v>
+      </c>
+      <c r="R129">
+        <v>1</v>
+      </c>
+      <c r="U129">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>85</v>
+      </c>
+      <c r="B130">
+        <v>29</v>
+      </c>
+      <c r="G130">
+        <v>4</v>
+      </c>
+      <c r="I130">
+        <v>1</v>
+      </c>
+      <c r="U130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>86</v>
+      </c>
+      <c r="B131">
+        <v>22</v>
+      </c>
+      <c r="I131">
+        <v>6</v>
+      </c>
+      <c r="P131">
+        <v>1</v>
+      </c>
+      <c r="U131">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>87</v>
+      </c>
+      <c r="B132">
+        <v>17</v>
+      </c>
+      <c r="I132">
+        <v>4</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="U132">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>88</v>
+      </c>
+      <c r="B133">
+        <v>52</v>
+      </c>
+      <c r="I133">
+        <v>17</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="R133">
+        <v>1</v>
+      </c>
+      <c r="S133">
+        <v>1</v>
+      </c>
+      <c r="U133">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="135" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A135" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B135" t="s">
+        <v>1</v>
+      </c>
+      <c r="C135" t="s">
+        <v>2</v>
+      </c>
+      <c r="D135" t="s">
+        <v>3</v>
+      </c>
+      <c r="E135" t="s">
+        <v>4</v>
+      </c>
+      <c r="F135" t="s">
+        <v>5</v>
+      </c>
+      <c r="G135" t="s">
+        <v>6</v>
+      </c>
+      <c r="H135" t="s">
+        <v>7</v>
+      </c>
+      <c r="I135" t="s">
+        <v>8</v>
+      </c>
+      <c r="J135" t="s">
+        <v>9</v>
+      </c>
+      <c r="K135" t="s">
+        <v>10</v>
+      </c>
+      <c r="L135" t="s">
+        <v>11</v>
+      </c>
+      <c r="M135" t="s">
+        <v>12</v>
+      </c>
+      <c r="N135" t="s">
+        <v>13</v>
+      </c>
+      <c r="O135" t="s">
+        <v>14</v>
+      </c>
+      <c r="P135" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q135" t="s">
+        <v>16</v>
+      </c>
+      <c r="R135" t="s">
+        <v>17</v>
+      </c>
+      <c r="S135" t="s">
+        <v>18</v>
+      </c>
+      <c r="T135" t="s">
+        <v>19</v>
+      </c>
+      <c r="U135" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="136" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A136" t="s">
+        <v>203</v>
+      </c>
+      <c r="B136">
+        <v>73</v>
+      </c>
+      <c r="G136">
+        <v>53</v>
+      </c>
+      <c r="H136">
+        <v>4</v>
+      </c>
+      <c r="U136">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A137" t="s">
+        <v>113</v>
+      </c>
+      <c r="B137">
+        <v>80</v>
+      </c>
+      <c r="C137">
+        <v>1</v>
+      </c>
+      <c r="G137">
+        <v>50</v>
+      </c>
+      <c r="H137">
+        <v>2</v>
+      </c>
+      <c r="I137">
+        <v>2</v>
+      </c>
+      <c r="J137">
+        <v>2</v>
+      </c>
+      <c r="N137">
+        <v>1</v>
+      </c>
+      <c r="U137">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>204</v>
+      </c>
+      <c r="B138">
+        <v>80</v>
+      </c>
+      <c r="G138">
+        <v>45</v>
+      </c>
+      <c r="H138">
+        <v>3</v>
+      </c>
+      <c r="I138">
+        <v>6</v>
+      </c>
+      <c r="U138">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>114</v>
+      </c>
+      <c r="B139">
+        <v>80</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="G139">
+        <v>81</v>
+      </c>
+      <c r="H139">
+        <v>7</v>
+      </c>
+      <c r="I139">
+        <v>4</v>
+      </c>
+      <c r="U139">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>205</v>
+      </c>
+      <c r="B140">
+        <v>80</v>
+      </c>
+      <c r="G140">
+        <v>29</v>
+      </c>
+      <c r="H140">
+        <v>1</v>
+      </c>
+      <c r="I140">
+        <v>2</v>
+      </c>
+      <c r="J140">
+        <v>1</v>
+      </c>
+      <c r="L140">
+        <v>1</v>
+      </c>
+      <c r="N140">
+        <v>1</v>
+      </c>
+      <c r="U140">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>118</v>
+      </c>
+      <c r="B141">
+        <v>7</v>
+      </c>
+      <c r="U141">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>167</v>
+      </c>
+      <c r="B142">
+        <v>80</v>
+      </c>
+      <c r="D142">
+        <v>1</v>
+      </c>
+      <c r="E142">
+        <v>1</v>
+      </c>
+      <c r="F142">
+        <v>2</v>
+      </c>
+      <c r="G142">
+        <v>6</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+      <c r="I142">
+        <v>4</v>
+      </c>
+      <c r="J142">
+        <v>1</v>
+      </c>
+      <c r="L142">
+        <v>1</v>
+      </c>
+      <c r="U142">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>120</v>
+      </c>
+      <c r="B143">
+        <v>57</v>
+      </c>
+      <c r="G143">
+        <v>8</v>
+      </c>
+      <c r="L143">
+        <v>6</v>
+      </c>
+      <c r="U143">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>177</v>
+      </c>
+      <c r="B144">
+        <v>23</v>
+      </c>
+      <c r="G144">
+        <v>9</v>
+      </c>
+      <c r="I144">
+        <v>2</v>
+      </c>
+      <c r="L144">
+        <v>2</v>
+      </c>
+      <c r="N144">
+        <v>1</v>
+      </c>
+      <c r="U144">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>206</v>
+      </c>
+      <c r="B145">
+        <v>5</v>
+      </c>
+      <c r="I145">
+        <v>2</v>
+      </c>
+      <c r="U145">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>122</v>
+      </c>
+      <c r="B146">
+        <v>73</v>
+      </c>
+      <c r="G146">
+        <v>56</v>
+      </c>
+      <c r="H146">
+        <v>6</v>
+      </c>
+      <c r="I146">
+        <v>8</v>
+      </c>
+      <c r="J146">
+        <v>2</v>
+      </c>
+      <c r="R146">
+        <v>3</v>
+      </c>
+      <c r="U146">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>123</v>
+      </c>
+      <c r="B147">
+        <v>75</v>
+      </c>
+      <c r="G147">
+        <v>30</v>
+      </c>
+      <c r="H147">
+        <v>4</v>
+      </c>
+      <c r="I147">
+        <v>13</v>
+      </c>
+      <c r="P147">
+        <v>1</v>
+      </c>
+      <c r="R147">
+        <v>3</v>
+      </c>
+      <c r="U147">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>124</v>
+      </c>
+      <c r="B148">
+        <v>7</v>
+      </c>
+      <c r="G148">
+        <v>4</v>
+      </c>
+      <c r="U148">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>125</v>
+      </c>
+      <c r="B149">
+        <v>56</v>
+      </c>
+      <c r="G149">
+        <v>3</v>
+      </c>
+      <c r="H149">
+        <v>2</v>
+      </c>
+      <c r="I149">
+        <v>9</v>
+      </c>
+      <c r="J149">
+        <v>1</v>
+      </c>
+      <c r="P149">
+        <v>1</v>
+      </c>
+      <c r="R149">
+        <v>3</v>
+      </c>
+      <c r="S149">
+        <v>1</v>
+      </c>
+      <c r="U149">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>126</v>
+      </c>
+      <c r="B150">
+        <v>13</v>
+      </c>
+      <c r="G150">
+        <v>25</v>
+      </c>
+      <c r="I150">
+        <v>2</v>
+      </c>
+      <c r="O150">
+        <v>1</v>
+      </c>
+      <c r="U150">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>127</v>
+      </c>
+      <c r="B151">
+        <v>80</v>
+      </c>
+      <c r="D151">
+        <v>1</v>
+      </c>
+      <c r="G151">
+        <v>3</v>
+      </c>
+      <c r="H151">
+        <v>1</v>
+      </c>
+      <c r="I151">
+        <v>15</v>
+      </c>
+      <c r="R151">
+        <v>3</v>
+      </c>
+      <c r="U151">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>128</v>
+      </c>
+      <c r="B152">
+        <v>69</v>
+      </c>
+      <c r="G152">
+        <v>1</v>
+      </c>
+      <c r="I152">
+        <v>10</v>
+      </c>
+      <c r="J152">
+        <v>2</v>
+      </c>
+      <c r="N152">
+        <v>1</v>
+      </c>
+      <c r="P152">
+        <v>3</v>
+      </c>
+      <c r="R152">
+        <v>3</v>
+      </c>
+      <c r="S152">
+        <v>1</v>
+      </c>
+      <c r="U152">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>129</v>
+      </c>
+      <c r="B153">
+        <v>13</v>
+      </c>
+      <c r="I153">
+        <v>2</v>
+      </c>
+      <c r="U153">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>130</v>
+      </c>
+      <c r="B154">
+        <v>57</v>
+      </c>
+      <c r="G154">
+        <v>5</v>
+      </c>
+      <c r="I154">
+        <v>6</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="R154">
+        <v>3</v>
+      </c>
+      <c r="U154">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>131</v>
+      </c>
+      <c r="B155">
+        <v>67</v>
+      </c>
+      <c r="G155">
+        <v>4</v>
+      </c>
+      <c r="I155">
+        <v>8</v>
+      </c>
+      <c r="R155">
+        <v>3</v>
+      </c>
+      <c r="U155">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>132</v>
+      </c>
+      <c r="B156">
+        <v>23</v>
+      </c>
+      <c r="G156">
+        <v>5</v>
+      </c>
+      <c r="I156">
+        <v>4</v>
+      </c>
+      <c r="U156">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>133</v>
+      </c>
+      <c r="B157">
+        <v>5</v>
+      </c>
+      <c r="G157">
+        <v>6</v>
+      </c>
+      <c r="I157">
+        <v>1</v>
+      </c>
+      <c r="U157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>134</v>
+      </c>
+      <c r="B158">
+        <v>75</v>
+      </c>
+      <c r="G158">
+        <v>10</v>
+      </c>
+      <c r="H158">
+        <v>1</v>
+      </c>
+      <c r="I158">
+        <v>7</v>
+      </c>
+      <c r="R158">
+        <v>3</v>
+      </c>
+      <c r="U158">
+        <v>13</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{255E43F5-9AC4-B743-B393-AC19A2B03340}">
+  <dimension ref="A1:U160"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A1" s="1" t="s">
+        <v>42</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>16</v>
+      </c>
+      <c r="R1" t="s">
+        <v>17</v>
+      </c>
+      <c r="S1" t="s">
+        <v>18</v>
+      </c>
+      <c r="T1" t="s">
+        <v>19</v>
+      </c>
+      <c r="U1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A2" t="s">
+        <v>158</v>
+      </c>
+      <c r="B2">
+        <v>65</v>
+      </c>
+      <c r="C2">
+        <v>1</v>
+      </c>
+      <c r="G2">
+        <v>28</v>
+      </c>
+      <c r="I2">
+        <v>3</v>
+      </c>
+      <c r="U2">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A3" t="s">
+        <v>43</v>
+      </c>
+      <c r="B3">
+        <v>80</v>
+      </c>
+      <c r="C3">
+        <v>2</v>
+      </c>
+      <c r="G3">
+        <v>77</v>
+      </c>
+      <c r="H3">
+        <v>1</v>
+      </c>
+      <c r="I3">
+        <v>2</v>
+      </c>
+      <c r="N3">
+        <v>1</v>
+      </c>
+      <c r="U3">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A4" t="s">
+        <v>44</v>
+      </c>
+      <c r="B4">
+        <v>80</v>
+      </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
+      <c r="G4">
+        <v>52</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>3</v>
+      </c>
+      <c r="U4">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A5" t="s">
+        <v>207</v>
+      </c>
+      <c r="B5">
+        <v>15</v>
+      </c>
+      <c r="G5">
+        <v>6</v>
+      </c>
+      <c r="I5">
+        <v>3</v>
+      </c>
+      <c r="U5">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A6" t="s">
+        <v>46</v>
+      </c>
+      <c r="B6">
+        <v>80</v>
+      </c>
+      <c r="D6">
+        <v>2</v>
+      </c>
+      <c r="G6">
+        <v>69</v>
+      </c>
+      <c r="H6">
+        <v>7</v>
+      </c>
+      <c r="I6">
+        <v>10</v>
+      </c>
+      <c r="J6">
+        <v>2</v>
+      </c>
+      <c r="U6">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A7" t="s">
+        <v>47</v>
+      </c>
+      <c r="B7">
+        <v>65</v>
+      </c>
+      <c r="G7">
+        <v>31</v>
+      </c>
+      <c r="I7">
+        <v>8</v>
+      </c>
+      <c r="N7">
+        <v>1</v>
+      </c>
+      <c r="U7">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A8" t="s">
+        <v>48</v>
+      </c>
+      <c r="B8">
+        <v>80</v>
+      </c>
+      <c r="D8">
+        <v>1</v>
+      </c>
+      <c r="E8">
+        <v>5</v>
+      </c>
+      <c r="F8">
+        <v>1</v>
+      </c>
+      <c r="G8">
+        <v>33</v>
+      </c>
+      <c r="I8">
+        <v>10</v>
+      </c>
+      <c r="L8">
+        <v>1</v>
+      </c>
+      <c r="U8">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A9" t="s">
+        <v>178</v>
+      </c>
+      <c r="B9">
+        <v>15</v>
+      </c>
+      <c r="D9">
+        <v>1</v>
+      </c>
+      <c r="G9">
+        <v>20</v>
+      </c>
+      <c r="I9">
+        <v>1</v>
+      </c>
+      <c r="N9">
+        <v>1</v>
+      </c>
+      <c r="U9">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A10" t="s">
+        <v>50</v>
+      </c>
+      <c r="B10">
+        <v>3</v>
+      </c>
+      <c r="I10">
+        <v>2</v>
+      </c>
+      <c r="U10">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A11" t="s">
+        <v>51</v>
+      </c>
+      <c r="B11">
+        <v>77</v>
+      </c>
+      <c r="G11">
+        <v>13</v>
+      </c>
+      <c r="I11">
+        <v>9</v>
+      </c>
+      <c r="L11">
+        <v>1</v>
+      </c>
+      <c r="U11">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A12" t="s">
+        <v>52</v>
+      </c>
+      <c r="B12">
+        <v>80</v>
+      </c>
+      <c r="G12">
+        <v>9</v>
+      </c>
+      <c r="H12">
+        <v>1</v>
+      </c>
+      <c r="I12">
+        <v>16</v>
+      </c>
+      <c r="R12">
+        <v>6</v>
+      </c>
+      <c r="U12">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A13" t="s">
+        <v>53</v>
+      </c>
+      <c r="B13">
+        <v>80</v>
+      </c>
+      <c r="G13">
+        <v>47</v>
+      </c>
+      <c r="H13">
+        <v>7</v>
+      </c>
+      <c r="I13">
+        <v>17</v>
+      </c>
+      <c r="J13">
+        <v>2</v>
+      </c>
+      <c r="Q13">
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <v>6</v>
+      </c>
+      <c r="U13">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A14" t="s">
+        <v>55</v>
+      </c>
+      <c r="B14">
+        <v>27</v>
+      </c>
+      <c r="G14">
+        <v>9</v>
+      </c>
+      <c r="H14">
+        <v>1</v>
+      </c>
+      <c r="I14">
+        <v>8</v>
+      </c>
+      <c r="U14">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A15" t="s">
+        <v>56</v>
+      </c>
+      <c r="B15">
+        <v>53</v>
+      </c>
+      <c r="G15">
+        <v>1</v>
+      </c>
+      <c r="I15">
+        <v>22</v>
+      </c>
+      <c r="R15">
+        <v>6</v>
+      </c>
+      <c r="U15">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A16" t="s">
+        <v>57</v>
+      </c>
+      <c r="B16">
+        <v>69</v>
+      </c>
+      <c r="G16">
+        <v>4</v>
+      </c>
+      <c r="I16">
+        <v>19</v>
+      </c>
+      <c r="P16">
+        <v>2</v>
+      </c>
+      <c r="R16">
+        <v>6</v>
+      </c>
+      <c r="U16">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A17" t="s">
+        <v>58</v>
+      </c>
+      <c r="B17">
+        <v>65</v>
+      </c>
+      <c r="G17">
+        <v>5</v>
+      </c>
+      <c r="I17">
+        <v>19</v>
+      </c>
+      <c r="J17">
+        <v>1</v>
+      </c>
+      <c r="O17">
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <v>6</v>
+      </c>
+      <c r="U17">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A18" t="s">
+        <v>208</v>
+      </c>
+      <c r="B18">
+        <v>26</v>
+      </c>
+      <c r="C18">
+        <v>1</v>
+      </c>
+      <c r="G18">
+        <v>2</v>
+      </c>
+      <c r="H18">
+        <v>1</v>
+      </c>
+      <c r="I18">
+        <v>10</v>
+      </c>
+      <c r="J18">
+        <v>1</v>
+      </c>
+      <c r="U18">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A19" t="s">
+        <v>60</v>
+      </c>
+      <c r="B19">
+        <v>15</v>
+      </c>
+      <c r="G19">
+        <v>5</v>
+      </c>
+      <c r="I19">
+        <v>4</v>
+      </c>
+      <c r="U19">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A20" t="s">
+        <v>162</v>
+      </c>
+      <c r="B20">
+        <v>65</v>
+      </c>
+      <c r="G20">
+        <v>3</v>
+      </c>
+      <c r="H20">
+        <v>1</v>
+      </c>
+      <c r="I20">
+        <v>16</v>
+      </c>
+      <c r="R20">
+        <v>6</v>
+      </c>
+      <c r="U20">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A21" t="s">
+        <v>63</v>
+      </c>
+      <c r="B21">
+        <v>15</v>
+      </c>
+      <c r="I21">
+        <v>4</v>
+      </c>
+      <c r="U21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A22" t="s">
+        <v>163</v>
+      </c>
+      <c r="B22">
+        <v>65</v>
+      </c>
+      <c r="G22">
+        <v>3</v>
+      </c>
+      <c r="I22">
+        <v>20</v>
+      </c>
+      <c r="J22">
+        <v>1</v>
+      </c>
+      <c r="N22">
+        <v>1</v>
+      </c>
+      <c r="P22">
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <v>6</v>
+      </c>
+      <c r="U22">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A23" t="s">
+        <v>64</v>
+      </c>
+      <c r="B23">
+        <v>15</v>
+      </c>
+      <c r="H23">
+        <v>1</v>
+      </c>
+      <c r="I23">
+        <v>6</v>
+      </c>
+      <c r="U23">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A24" t="s">
+        <v>65</v>
+      </c>
+      <c r="B24">
+        <v>65</v>
+      </c>
+      <c r="C24">
+        <v>1</v>
+      </c>
+      <c r="G24">
+        <v>24</v>
+      </c>
+      <c r="H24">
+        <v>1</v>
+      </c>
+      <c r="I24">
+        <v>18</v>
+      </c>
+      <c r="R24">
+        <v>6</v>
+      </c>
+      <c r="U24">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A27" s="1" t="s">
+        <v>89</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1</v>
+      </c>
+      <c r="C27" t="s">
+        <v>2</v>
+      </c>
+      <c r="D27" t="s">
+        <v>3</v>
+      </c>
+      <c r="E27" t="s">
+        <v>4</v>
+      </c>
+      <c r="F27" t="s">
+        <v>5</v>
+      </c>
+      <c r="G27" t="s">
+        <v>6</v>
+      </c>
+      <c r="H27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I27" t="s">
+        <v>8</v>
+      </c>
+      <c r="J27" t="s">
+        <v>9</v>
+      </c>
+      <c r="K27" t="s">
+        <v>10</v>
+      </c>
+      <c r="L27" t="s">
+        <v>11</v>
+      </c>
+      <c r="M27" t="s">
+        <v>12</v>
+      </c>
+      <c r="N27" t="s">
+        <v>13</v>
+      </c>
+      <c r="O27" t="s">
+        <v>14</v>
+      </c>
+      <c r="P27" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>16</v>
+      </c>
+      <c r="R27" t="s">
+        <v>17</v>
+      </c>
+      <c r="S27" t="s">
+        <v>18</v>
+      </c>
+      <c r="T27" t="s">
+        <v>19</v>
+      </c>
+      <c r="U27" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A28" t="s">
+        <v>90</v>
+      </c>
+      <c r="B28">
+        <v>62</v>
+      </c>
+      <c r="C28">
+        <v>1</v>
+      </c>
+      <c r="G28">
+        <v>39</v>
+      </c>
+      <c r="H28">
+        <v>4</v>
+      </c>
+      <c r="I28">
+        <v>7</v>
+      </c>
+      <c r="J28">
+        <v>1</v>
+      </c>
+      <c r="L28">
+        <v>1</v>
+      </c>
+      <c r="N28">
+        <v>1</v>
+      </c>
+      <c r="U28">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A29" t="s">
+        <v>184</v>
+      </c>
+      <c r="B29">
+        <v>80</v>
+      </c>
+      <c r="D29">
+        <v>1</v>
+      </c>
+      <c r="G29">
+        <v>22</v>
+      </c>
+      <c r="H29">
+        <v>3</v>
+      </c>
+      <c r="I29">
+        <v>3</v>
+      </c>
+      <c r="N29">
+        <v>2</v>
+      </c>
+      <c r="U29">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A30" t="s">
+        <v>209</v>
+      </c>
+      <c r="B30">
+        <v>7</v>
+      </c>
+      <c r="I30">
+        <v>1</v>
+      </c>
+      <c r="U30">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A31" t="s">
+        <v>91</v>
+      </c>
+      <c r="B31">
+        <v>80</v>
+      </c>
+      <c r="G31">
+        <v>45</v>
+      </c>
+      <c r="H31">
+        <v>6</v>
+      </c>
+      <c r="I31">
+        <v>5</v>
+      </c>
+      <c r="J31">
+        <v>1</v>
+      </c>
+      <c r="N31">
+        <v>1</v>
+      </c>
+      <c r="U31">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A32" t="s">
+        <v>92</v>
+      </c>
+      <c r="B32">
+        <v>80</v>
+      </c>
+      <c r="G32">
+        <v>6</v>
+      </c>
+      <c r="H32">
+        <v>1</v>
+      </c>
+      <c r="I32">
+        <v>10</v>
+      </c>
+      <c r="N32">
+        <v>1</v>
+      </c>
+      <c r="U32">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A33" t="s">
+        <v>93</v>
+      </c>
+      <c r="B33">
+        <v>11</v>
+      </c>
+      <c r="G33">
+        <v>5</v>
+      </c>
+      <c r="U33">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A34" t="s">
+        <v>94</v>
+      </c>
+      <c r="B34">
+        <v>80</v>
+      </c>
+      <c r="G34">
+        <v>29</v>
+      </c>
+      <c r="H34">
+        <v>3</v>
+      </c>
+      <c r="I34">
+        <v>9</v>
+      </c>
+      <c r="N34">
+        <v>1</v>
+      </c>
+      <c r="U34">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A35" t="s">
+        <v>95</v>
+      </c>
+      <c r="B35">
+        <v>80</v>
+      </c>
+      <c r="C35">
+        <v>1</v>
+      </c>
+      <c r="E35">
+        <v>3</v>
+      </c>
+      <c r="G35">
+        <v>32</v>
+      </c>
+      <c r="H35">
+        <v>1</v>
+      </c>
+      <c r="I35">
+        <v>10</v>
+      </c>
+      <c r="L35">
+        <v>1</v>
+      </c>
+      <c r="N35">
+        <v>2</v>
+      </c>
+      <c r="U35">
+        <v>37</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A36" t="s">
+        <v>96</v>
+      </c>
+      <c r="B36">
+        <v>18</v>
+      </c>
+      <c r="G36">
+        <v>5</v>
+      </c>
+      <c r="H36">
+        <v>1</v>
+      </c>
+      <c r="I36">
+        <v>1</v>
+      </c>
+      <c r="U36">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A37" t="s">
+        <v>97</v>
+      </c>
+      <c r="B37">
+        <v>62</v>
+      </c>
+      <c r="D37">
+        <v>1</v>
+      </c>
+      <c r="G37">
+        <v>9</v>
+      </c>
+      <c r="H37">
+        <v>1</v>
+      </c>
+      <c r="I37">
+        <v>8</v>
+      </c>
+      <c r="L37">
+        <v>2</v>
+      </c>
+      <c r="N37">
+        <v>1</v>
+      </c>
+      <c r="U37">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A38" t="s">
+        <v>210</v>
+      </c>
+      <c r="B38">
+        <v>18</v>
+      </c>
+      <c r="G38">
+        <v>4</v>
+      </c>
+      <c r="I38">
+        <v>7</v>
+      </c>
+      <c r="R38">
+        <v>1</v>
+      </c>
+      <c r="U38">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A39" t="s">
+        <v>98</v>
+      </c>
+      <c r="B39">
+        <v>80</v>
+      </c>
+      <c r="C39">
+        <v>1</v>
+      </c>
+      <c r="G39">
+        <v>34</v>
+      </c>
+      <c r="H39">
+        <v>4</v>
+      </c>
+      <c r="I39">
+        <v>18</v>
+      </c>
+      <c r="N39">
+        <v>1</v>
+      </c>
+      <c r="R39">
+        <v>2</v>
+      </c>
+      <c r="U39">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A40" t="s">
+        <v>99</v>
+      </c>
+      <c r="B40">
+        <v>62</v>
+      </c>
+      <c r="G40">
+        <v>35</v>
+      </c>
+      <c r="H40">
+        <v>1</v>
+      </c>
+      <c r="I40">
+        <v>10</v>
+      </c>
+      <c r="R40">
+        <v>1</v>
+      </c>
+      <c r="U40">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A41" t="s">
+        <v>100</v>
+      </c>
+      <c r="B41">
+        <v>80</v>
+      </c>
+      <c r="G41">
+        <v>7</v>
+      </c>
+      <c r="I41">
+        <v>16</v>
+      </c>
+      <c r="R41">
+        <v>2</v>
+      </c>
+      <c r="U41">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A42" t="s">
+        <v>211</v>
+      </c>
+      <c r="B42">
+        <v>18</v>
+      </c>
+      <c r="G42">
+        <v>2</v>
+      </c>
+      <c r="I42">
+        <v>5</v>
+      </c>
+      <c r="J42">
+        <v>1</v>
+      </c>
+      <c r="R42">
+        <v>1</v>
+      </c>
+      <c r="U42">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A43" t="s">
+        <v>103</v>
+      </c>
+      <c r="B43">
+        <v>80</v>
+      </c>
+      <c r="D43">
+        <v>1</v>
+      </c>
+      <c r="G43">
+        <v>6</v>
+      </c>
+      <c r="I43">
+        <v>19</v>
+      </c>
+      <c r="J43">
+        <v>1</v>
+      </c>
+      <c r="R43">
+        <v>2</v>
+      </c>
+      <c r="U43">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A44" t="s">
+        <v>104</v>
+      </c>
+      <c r="B44">
+        <v>62</v>
+      </c>
+      <c r="G44">
+        <v>5</v>
+      </c>
+      <c r="I44">
+        <v>11</v>
+      </c>
+      <c r="R44">
+        <v>1</v>
+      </c>
+      <c r="U44">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A45" t="s">
+        <v>105</v>
+      </c>
+      <c r="B45">
+        <v>69</v>
+      </c>
+      <c r="G45">
+        <v>14</v>
+      </c>
+      <c r="H45">
+        <v>2</v>
+      </c>
+      <c r="I45">
+        <v>12</v>
+      </c>
+      <c r="J45">
+        <v>2</v>
+      </c>
+      <c r="R45">
+        <v>2</v>
+      </c>
+      <c r="U45">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A46" t="s">
+        <v>199</v>
+      </c>
+      <c r="B46">
+        <v>11</v>
+      </c>
+      <c r="U46">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A47" t="s">
+        <v>108</v>
+      </c>
+      <c r="B47">
+        <v>69</v>
+      </c>
+      <c r="G47">
+        <v>15</v>
+      </c>
+      <c r="I47">
+        <v>13</v>
+      </c>
+      <c r="R47">
+        <v>2</v>
+      </c>
+      <c r="U47">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A48" t="s">
+        <v>200</v>
+      </c>
+      <c r="B48">
+        <v>11</v>
+      </c>
+      <c r="U48">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A49" t="s">
+        <v>109</v>
+      </c>
+      <c r="B49">
+        <v>62</v>
+      </c>
+      <c r="G49">
+        <v>18</v>
+      </c>
+      <c r="I49">
+        <v>12</v>
+      </c>
+      <c r="J49">
+        <v>1</v>
+      </c>
+      <c r="R49">
+        <v>2</v>
+      </c>
+      <c r="U49">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A50" t="s">
+        <v>110</v>
+      </c>
+      <c r="B50">
+        <v>18</v>
+      </c>
+      <c r="G50">
+        <v>11</v>
+      </c>
+      <c r="I50">
+        <v>3</v>
+      </c>
+      <c r="U50">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A58" s="1" t="s">
+        <v>135</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1</v>
+      </c>
+      <c r="C58" t="s">
+        <v>2</v>
+      </c>
+      <c r="D58" t="s">
+        <v>3</v>
+      </c>
+      <c r="E58" t="s">
+        <v>4</v>
+      </c>
+      <c r="F58" t="s">
+        <v>5</v>
+      </c>
+      <c r="G58" t="s">
+        <v>6</v>
+      </c>
+      <c r="H58" t="s">
+        <v>7</v>
+      </c>
+      <c r="I58" t="s">
+        <v>8</v>
+      </c>
+      <c r="J58" t="s">
+        <v>9</v>
+      </c>
+      <c r="K58" t="s">
+        <v>10</v>
+      </c>
+      <c r="L58" t="s">
+        <v>11</v>
+      </c>
+      <c r="M58" t="s">
+        <v>12</v>
+      </c>
+      <c r="N58" t="s">
+        <v>13</v>
+      </c>
+      <c r="O58" t="s">
+        <v>14</v>
+      </c>
+      <c r="P58" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>16</v>
+      </c>
+      <c r="R58" t="s">
+        <v>17</v>
+      </c>
+      <c r="S58" t="s">
+        <v>18</v>
+      </c>
+      <c r="T58" t="s">
+        <v>19</v>
+      </c>
+      <c r="U58" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A59" t="s">
+        <v>136</v>
+      </c>
+      <c r="B59">
+        <v>80</v>
+      </c>
+      <c r="G59">
+        <v>78</v>
+      </c>
+      <c r="H59">
+        <v>6</v>
+      </c>
+      <c r="I59">
+        <v>5</v>
+      </c>
+      <c r="N59">
+        <v>2</v>
+      </c>
+      <c r="U59">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A60" t="s">
+        <v>137</v>
+      </c>
+      <c r="B60">
+        <v>78</v>
+      </c>
+      <c r="G60">
+        <v>28</v>
+      </c>
+      <c r="H60">
+        <v>3</v>
+      </c>
+      <c r="I60">
+        <v>7</v>
+      </c>
+      <c r="J60">
+        <v>1</v>
+      </c>
+      <c r="P60">
+        <v>1</v>
+      </c>
+      <c r="U60">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A61" t="s">
+        <v>180</v>
+      </c>
+      <c r="B61">
+        <v>2</v>
+      </c>
+      <c r="U61">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A62" t="s">
+        <v>138</v>
+      </c>
+      <c r="B62">
+        <v>80</v>
+      </c>
+      <c r="G62">
+        <v>68</v>
+      </c>
+      <c r="H62">
+        <v>4</v>
+      </c>
+      <c r="I62">
+        <v>3</v>
+      </c>
+      <c r="N62">
+        <v>1</v>
+      </c>
+      <c r="U62">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A63" t="s">
+        <v>168</v>
+      </c>
+      <c r="B63">
+        <v>80</v>
+      </c>
+      <c r="D63">
+        <v>1</v>
+      </c>
+      <c r="G63">
+        <v>28</v>
+      </c>
+      <c r="H63">
+        <v>1</v>
+      </c>
+      <c r="I63">
+        <v>7</v>
+      </c>
+      <c r="P63">
+        <v>1</v>
+      </c>
+      <c r="U63">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A64" t="s">
+        <v>140</v>
+      </c>
+      <c r="B64">
+        <v>80</v>
+      </c>
+      <c r="G64">
+        <v>51</v>
+      </c>
+      <c r="I64">
+        <v>7</v>
+      </c>
+      <c r="J64">
+        <v>1</v>
+      </c>
+      <c r="U64">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A65" t="s">
+        <v>142</v>
+      </c>
+      <c r="B65">
+        <v>67</v>
+      </c>
+      <c r="C65">
+        <v>1</v>
+      </c>
+      <c r="E65">
+        <v>4</v>
+      </c>
+      <c r="G65">
+        <v>25</v>
+      </c>
+      <c r="H65">
+        <v>4</v>
+      </c>
+      <c r="I65">
+        <v>2</v>
+      </c>
+      <c r="M65">
+        <v>1</v>
+      </c>
+      <c r="U65">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A66" t="s">
+        <v>169</v>
+      </c>
+      <c r="B66">
+        <v>13</v>
+      </c>
+      <c r="I66">
+        <v>1</v>
+      </c>
+      <c r="U66">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A67" t="s">
+        <v>143</v>
+      </c>
+      <c r="B67">
+        <v>2</v>
+      </c>
+      <c r="I67">
+        <v>1</v>
+      </c>
+      <c r="U67">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A68" t="s">
+        <v>144</v>
+      </c>
+      <c r="B68">
+        <v>78</v>
+      </c>
+      <c r="D68">
+        <v>1</v>
+      </c>
+      <c r="G68">
+        <v>7</v>
+      </c>
+      <c r="H68">
+        <v>3</v>
+      </c>
+      <c r="I68">
+        <v>4</v>
+      </c>
+      <c r="N68">
+        <v>1</v>
+      </c>
+      <c r="O68">
+        <v>1</v>
+      </c>
+      <c r="U68">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A69" t="s">
+        <v>182</v>
+      </c>
+      <c r="B69">
+        <v>80</v>
+      </c>
+      <c r="G69">
+        <v>24</v>
+      </c>
+      <c r="H69">
+        <v>1</v>
+      </c>
+      <c r="I69">
+        <v>17</v>
+      </c>
+      <c r="R69">
+        <v>4</v>
+      </c>
+      <c r="U69">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A70" t="s">
+        <v>170</v>
+      </c>
+      <c r="B70">
+        <v>9</v>
+      </c>
+      <c r="I70">
+        <v>5</v>
+      </c>
+      <c r="R70">
+        <v>1</v>
+      </c>
+      <c r="U70">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A71" t="s">
+        <v>147</v>
+      </c>
+      <c r="B71">
+        <v>71</v>
+      </c>
+      <c r="G71">
+        <v>18</v>
+      </c>
+      <c r="H71">
+        <v>2</v>
+      </c>
+      <c r="I71">
+        <v>11</v>
+      </c>
+      <c r="J71">
+        <v>2</v>
+      </c>
+      <c r="R71">
+        <v>3</v>
+      </c>
+      <c r="U71">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A72" t="s">
+        <v>148</v>
+      </c>
+      <c r="B72">
+        <v>80</v>
+      </c>
+      <c r="C72">
+        <v>2</v>
+      </c>
+      <c r="G72">
+        <v>32</v>
+      </c>
+      <c r="H72">
+        <v>5</v>
+      </c>
+      <c r="I72">
+        <v>6</v>
+      </c>
+      <c r="Q72">
+        <v>1</v>
+      </c>
+      <c r="R72">
+        <v>4</v>
+      </c>
+      <c r="U72">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A73" t="s">
+        <v>149</v>
+      </c>
+      <c r="B73">
+        <v>16</v>
+      </c>
+      <c r="I73">
+        <v>2</v>
+      </c>
+      <c r="R73">
+        <v>1</v>
+      </c>
+      <c r="U73">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A74" t="s">
+        <v>150</v>
+      </c>
+      <c r="B74">
+        <v>64</v>
+      </c>
+      <c r="G74">
+        <v>12</v>
+      </c>
+      <c r="H74">
+        <v>1</v>
+      </c>
+      <c r="I74">
+        <v>6</v>
+      </c>
+      <c r="R74">
+        <v>3</v>
+      </c>
+      <c r="U74">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A75" t="s">
+        <v>151</v>
+      </c>
+      <c r="B75">
+        <v>80</v>
+      </c>
+      <c r="I75">
+        <v>11</v>
+      </c>
+      <c r="R75">
+        <v>4</v>
+      </c>
+      <c r="U75">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A76" t="s">
+        <v>152</v>
+      </c>
+      <c r="B76">
+        <v>51</v>
+      </c>
+      <c r="G76">
+        <v>8</v>
+      </c>
+      <c r="I76">
+        <v>7</v>
+      </c>
+      <c r="J76">
+        <v>1</v>
+      </c>
+      <c r="N76">
+        <v>1</v>
+      </c>
+      <c r="P76">
+        <v>1</v>
+      </c>
+      <c r="R76">
+        <v>3</v>
+      </c>
+      <c r="U76">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A77" t="s">
+        <v>153</v>
+      </c>
+      <c r="B77">
+        <v>37</v>
+      </c>
+      <c r="I77">
+        <v>3</v>
+      </c>
+      <c r="R77">
+        <v>3</v>
+      </c>
+      <c r="U77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A78" t="s">
+        <v>154</v>
+      </c>
+      <c r="B78">
+        <v>32</v>
+      </c>
+      <c r="G78">
+        <v>1</v>
+      </c>
+      <c r="I78">
+        <v>7</v>
+      </c>
+      <c r="R78">
+        <v>1</v>
+      </c>
+      <c r="S78">
+        <v>1</v>
+      </c>
+      <c r="U78">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A79" t="s">
+        <v>155</v>
+      </c>
+      <c r="B79">
+        <v>29</v>
+      </c>
+      <c r="I79">
+        <v>7</v>
+      </c>
+      <c r="J79">
+        <v>2</v>
+      </c>
+      <c r="R79">
+        <v>1</v>
+      </c>
+      <c r="U79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A80" t="s">
+        <v>171</v>
+      </c>
+      <c r="B80">
+        <v>35</v>
+      </c>
+      <c r="G80">
+        <v>5</v>
+      </c>
+      <c r="I80">
+        <v>9</v>
+      </c>
+      <c r="R80">
+        <v>1</v>
+      </c>
+      <c r="U80">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A81" t="s">
+        <v>157</v>
+      </c>
+      <c r="B81">
+        <v>45</v>
+      </c>
+      <c r="C81">
+        <v>1</v>
+      </c>
+      <c r="G81">
+        <v>8</v>
+      </c>
+      <c r="H81">
+        <v>1</v>
+      </c>
+      <c r="I81">
+        <v>5</v>
+      </c>
+      <c r="N81">
+        <v>1</v>
+      </c>
+      <c r="P81">
+        <v>1</v>
+      </c>
+      <c r="R81">
+        <v>3</v>
+      </c>
+      <c r="U81">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A84" s="1" t="s">
+        <v>66</v>
+      </c>
+      <c r="B84" t="s">
+        <v>1</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2</v>
+      </c>
+      <c r="D84" t="s">
+        <v>3</v>
+      </c>
+      <c r="E84" t="s">
+        <v>4</v>
+      </c>
+      <c r="F84" t="s">
+        <v>5</v>
+      </c>
+      <c r="G84" t="s">
+        <v>6</v>
+      </c>
+      <c r="H84" t="s">
+        <v>7</v>
+      </c>
+      <c r="I84" t="s">
+        <v>8</v>
+      </c>
+      <c r="J84" t="s">
+        <v>9</v>
+      </c>
+      <c r="K84" t="s">
+        <v>10</v>
+      </c>
+      <c r="L84" t="s">
+        <v>11</v>
+      </c>
+      <c r="M84" t="s">
+        <v>12</v>
+      </c>
+      <c r="N84" t="s">
+        <v>13</v>
+      </c>
+      <c r="O84" t="s">
+        <v>14</v>
+      </c>
+      <c r="P84" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>16</v>
+      </c>
+      <c r="R84" t="s">
+        <v>17</v>
+      </c>
+      <c r="S84" t="s">
+        <v>18</v>
+      </c>
+      <c r="T84" t="s">
+        <v>19</v>
+      </c>
+      <c r="U84" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A85" t="s">
+        <v>67</v>
+      </c>
+      <c r="B85">
+        <v>80</v>
+      </c>
+      <c r="G85">
+        <v>49</v>
+      </c>
+      <c r="H85">
+        <v>3</v>
+      </c>
+      <c r="I85">
+        <v>5</v>
+      </c>
+      <c r="J85">
+        <v>2</v>
+      </c>
+      <c r="U85">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A86" t="s">
+        <v>68</v>
+      </c>
+      <c r="B86">
+        <v>80</v>
+      </c>
+      <c r="G86">
+        <v>28</v>
+      </c>
+      <c r="H86">
+        <v>1</v>
+      </c>
+      <c r="I86">
+        <v>6</v>
+      </c>
+      <c r="U86">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A87" t="s">
+        <v>69</v>
+      </c>
+      <c r="B87">
+        <v>63</v>
+      </c>
+      <c r="G87">
+        <v>20</v>
+      </c>
+      <c r="H87">
+        <v>1</v>
+      </c>
+      <c r="I87">
+        <v>1</v>
+      </c>
+      <c r="J87">
+        <v>2</v>
+      </c>
+      <c r="U87">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A88" t="s">
+        <v>70</v>
+      </c>
+      <c r="B88">
+        <v>70</v>
+      </c>
+      <c r="G88">
+        <v>7</v>
+      </c>
+      <c r="I88">
+        <v>8</v>
+      </c>
+      <c r="U88">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A89" t="s">
+        <v>71</v>
+      </c>
+      <c r="B89">
+        <v>80</v>
+      </c>
+      <c r="G89">
+        <v>108</v>
+      </c>
+      <c r="H89">
+        <v>6</v>
+      </c>
+      <c r="I89">
+        <v>13</v>
+      </c>
+      <c r="N89">
+        <v>2</v>
+      </c>
+      <c r="P89">
+        <v>1</v>
+      </c>
+      <c r="U89">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A90" t="s">
+        <v>202</v>
+      </c>
+      <c r="B90">
+        <v>17</v>
+      </c>
+      <c r="C90">
+        <v>1</v>
+      </c>
+      <c r="G90">
+        <v>33</v>
+      </c>
+      <c r="U90">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A91" t="s">
+        <v>72</v>
+      </c>
+      <c r="B91">
+        <v>80</v>
+      </c>
+      <c r="C91">
+        <v>1</v>
+      </c>
+      <c r="D91">
+        <v>1</v>
+      </c>
+      <c r="E91">
+        <v>1</v>
+      </c>
+      <c r="G91">
+        <v>27</v>
+      </c>
+      <c r="H91">
+        <v>1</v>
+      </c>
+      <c r="I91">
+        <v>4</v>
+      </c>
+      <c r="L91">
+        <v>4</v>
+      </c>
+      <c r="N91">
+        <v>1</v>
+      </c>
+      <c r="U91">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A92" t="s">
+        <v>73</v>
+      </c>
+      <c r="B92">
+        <v>10</v>
+      </c>
+      <c r="G92">
+        <v>12</v>
+      </c>
+      <c r="N92">
+        <v>1</v>
+      </c>
+      <c r="U92">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A93" t="s">
+        <v>74</v>
+      </c>
+      <c r="B93">
+        <v>53</v>
+      </c>
+      <c r="G93">
+        <v>16</v>
+      </c>
+      <c r="H93">
+        <v>2</v>
+      </c>
+      <c r="I93">
+        <v>2</v>
+      </c>
+      <c r="J93">
+        <v>1</v>
+      </c>
+      <c r="U93">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A94" t="s">
+        <v>212</v>
+      </c>
+      <c r="B94">
+        <v>27</v>
+      </c>
+      <c r="G94">
+        <v>30</v>
+      </c>
+      <c r="I94">
+        <v>1</v>
+      </c>
+      <c r="L94">
+        <v>1</v>
+      </c>
+      <c r="U94">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A95" t="s">
+        <v>76</v>
+      </c>
+      <c r="B95">
+        <v>63</v>
+      </c>
+      <c r="G95">
+        <v>62</v>
+      </c>
+      <c r="H95">
+        <v>1</v>
+      </c>
+      <c r="I95">
+        <v>10</v>
+      </c>
+      <c r="P95">
+        <v>1</v>
+      </c>
+      <c r="R95">
+        <v>2</v>
+      </c>
+      <c r="U95">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A96" t="s">
+        <v>77</v>
+      </c>
+      <c r="B96">
+        <v>80</v>
+      </c>
+      <c r="D96">
+        <v>1</v>
+      </c>
+      <c r="G96">
+        <v>10</v>
+      </c>
+      <c r="I96">
+        <v>8</v>
+      </c>
+      <c r="N96">
+        <v>1</v>
+      </c>
+      <c r="P96">
+        <v>1</v>
+      </c>
+      <c r="R96">
+        <v>6</v>
+      </c>
+      <c r="U96">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A97" t="s">
+        <v>165</v>
+      </c>
+      <c r="B97">
+        <v>17</v>
+      </c>
+      <c r="G97">
+        <v>15</v>
+      </c>
+      <c r="I97">
+        <v>2</v>
+      </c>
+      <c r="N97">
+        <v>1</v>
+      </c>
+      <c r="R97">
+        <v>4</v>
+      </c>
+      <c r="U97">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A98" t="s">
+        <v>78</v>
+      </c>
+      <c r="B98">
+        <v>80</v>
+      </c>
+      <c r="G98">
+        <v>2</v>
+      </c>
+      <c r="H98">
+        <v>1</v>
+      </c>
+      <c r="I98">
+        <v>12</v>
+      </c>
+      <c r="J98">
+        <v>2</v>
+      </c>
+      <c r="R98">
+        <v>6</v>
+      </c>
+      <c r="U98">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A99" t="s">
+        <v>79</v>
+      </c>
+      <c r="B99">
+        <v>70</v>
+      </c>
+      <c r="I99">
+        <v>9</v>
+      </c>
+      <c r="R99">
+        <v>3</v>
+      </c>
+      <c r="U99">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A100" t="s">
+        <v>80</v>
+      </c>
+      <c r="B100">
+        <v>10</v>
+      </c>
+      <c r="G100">
+        <v>6</v>
+      </c>
+      <c r="H100">
+        <v>1</v>
+      </c>
+      <c r="I100">
+        <v>1</v>
+      </c>
+      <c r="N100">
+        <v>1</v>
+      </c>
+      <c r="R100">
+        <v>3</v>
+      </c>
+      <c r="U100">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A101" t="s">
+        <v>81</v>
+      </c>
+      <c r="B101">
+        <v>80</v>
+      </c>
+      <c r="G101">
+        <v>15</v>
+      </c>
+      <c r="I101">
+        <v>11</v>
+      </c>
+      <c r="O101">
+        <v>1</v>
+      </c>
+      <c r="R101">
+        <v>6</v>
+      </c>
+      <c r="U101">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="102" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A102" t="s">
+        <v>84</v>
+      </c>
+      <c r="B102">
+        <v>47</v>
+      </c>
+      <c r="G102">
+        <v>9</v>
+      </c>
+      <c r="I102">
+        <v>11</v>
+      </c>
+      <c r="J102">
+        <v>1</v>
+      </c>
+      <c r="N102">
+        <v>1</v>
+      </c>
+      <c r="R102">
+        <v>3</v>
+      </c>
+      <c r="U102">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="103" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A103" t="s">
+        <v>85</v>
+      </c>
+      <c r="B103">
+        <v>45</v>
+      </c>
+      <c r="I103">
+        <v>10</v>
+      </c>
+      <c r="R103">
+        <v>2</v>
+      </c>
+      <c r="U103">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="104" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A104" t="s">
+        <v>86</v>
+      </c>
+      <c r="B104">
+        <v>33</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="I104">
+        <v>3</v>
+      </c>
+      <c r="R104">
+        <v>3</v>
+      </c>
+      <c r="U104">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="105" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A105" t="s">
+        <v>192</v>
+      </c>
+      <c r="B105">
+        <v>35</v>
+      </c>
+      <c r="I105">
+        <v>5</v>
+      </c>
+      <c r="J105">
+        <v>1</v>
+      </c>
+      <c r="R105">
+        <v>4</v>
+      </c>
+      <c r="U105">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="106" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A106" t="s">
+        <v>87</v>
+      </c>
+      <c r="B106">
+        <v>16</v>
+      </c>
+      <c r="C106">
+        <v>1</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="I106">
+        <v>3</v>
+      </c>
+      <c r="U106">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="107" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A107" t="s">
+        <v>88</v>
+      </c>
+      <c r="B107">
+        <v>64</v>
+      </c>
+      <c r="G107">
+        <v>17</v>
+      </c>
+      <c r="I107">
+        <v>13</v>
+      </c>
+      <c r="J107">
+        <v>1</v>
+      </c>
+      <c r="R107">
+        <v>6</v>
+      </c>
+      <c r="U107">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="113" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A113" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B113" t="s">
+        <v>1</v>
+      </c>
+      <c r="C113" t="s">
+        <v>2</v>
+      </c>
+      <c r="D113" t="s">
+        <v>3</v>
+      </c>
+      <c r="E113" t="s">
+        <v>4</v>
+      </c>
+      <c r="F113" t="s">
+        <v>5</v>
+      </c>
+      <c r="G113" t="s">
+        <v>6</v>
+      </c>
+      <c r="H113" t="s">
+        <v>7</v>
+      </c>
+      <c r="I113" t="s">
+        <v>8</v>
+      </c>
+      <c r="J113" t="s">
+        <v>9</v>
+      </c>
+      <c r="K113" t="s">
+        <v>10</v>
+      </c>
+      <c r="L113" t="s">
+        <v>11</v>
+      </c>
+      <c r="M113" t="s">
+        <v>12</v>
+      </c>
+      <c r="N113" t="s">
+        <v>13</v>
+      </c>
+      <c r="O113" t="s">
+        <v>14</v>
+      </c>
+      <c r="P113" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q113" t="s">
+        <v>16</v>
+      </c>
+      <c r="R113" t="s">
+        <v>17</v>
+      </c>
+      <c r="S113" t="s">
+        <v>18</v>
+      </c>
+      <c r="T113" t="s">
+        <v>19</v>
+      </c>
+      <c r="U113" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="114" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A114" t="s">
+        <v>21</v>
+      </c>
+      <c r="B114">
+        <v>80</v>
+      </c>
+      <c r="C114">
+        <v>1</v>
+      </c>
+      <c r="G114">
+        <v>48</v>
+      </c>
+      <c r="H114">
+        <v>2</v>
+      </c>
+      <c r="I114">
+        <v>10</v>
+      </c>
+      <c r="N114">
+        <v>1</v>
+      </c>
+      <c r="U114">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="115" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A115" t="s">
+        <v>22</v>
+      </c>
+      <c r="B115">
+        <v>80</v>
+      </c>
+      <c r="C115">
+        <v>4</v>
+      </c>
+      <c r="G115">
+        <v>47</v>
+      </c>
+      <c r="H115">
+        <v>3</v>
+      </c>
+      <c r="I115">
+        <v>2</v>
+      </c>
+      <c r="J115">
+        <v>1</v>
+      </c>
+      <c r="L115">
+        <v>1</v>
+      </c>
+      <c r="Q115">
+        <v>1</v>
+      </c>
+      <c r="U115">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="116" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A116" t="s">
+        <v>23</v>
+      </c>
+      <c r="B116">
+        <v>80</v>
+      </c>
+      <c r="D116">
+        <v>1</v>
+      </c>
+      <c r="E116">
+        <v>5</v>
+      </c>
+      <c r="F116">
+        <v>2</v>
+      </c>
+      <c r="G116">
+        <v>36</v>
+      </c>
+      <c r="I116">
+        <v>1</v>
+      </c>
+      <c r="L116">
+        <v>2</v>
+      </c>
+      <c r="N116">
+        <v>1</v>
+      </c>
+      <c r="U116">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="117" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A117" t="s">
+        <v>189</v>
+      </c>
+      <c r="B117">
+        <v>80</v>
+      </c>
+      <c r="G117">
+        <v>14</v>
+      </c>
+      <c r="H117">
+        <v>1</v>
+      </c>
+      <c r="I117">
+        <v>8</v>
+      </c>
+      <c r="J117">
+        <v>1</v>
+      </c>
+      <c r="N117">
+        <v>1</v>
+      </c>
+      <c r="U117">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="118" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A118" t="s">
+        <v>26</v>
+      </c>
+      <c r="B118">
+        <v>80</v>
+      </c>
+      <c r="G118">
+        <v>27</v>
+      </c>
+      <c r="H118">
+        <v>1</v>
+      </c>
+      <c r="I118">
+        <v>6</v>
+      </c>
+      <c r="N118">
+        <v>2</v>
+      </c>
+      <c r="U118">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="119" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A119" t="s">
+        <v>27</v>
+      </c>
+      <c r="B119">
+        <v>80</v>
+      </c>
+      <c r="D119">
+        <v>1</v>
+      </c>
+      <c r="G119">
+        <v>64</v>
+      </c>
+      <c r="H119">
+        <v>7</v>
+      </c>
+      <c r="I119">
+        <v>8</v>
+      </c>
+      <c r="L119">
+        <v>3</v>
+      </c>
+      <c r="N119">
+        <v>3</v>
+      </c>
+      <c r="U119">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="120" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A120" t="s">
+        <v>28</v>
+      </c>
+      <c r="B120">
+        <v>80</v>
+      </c>
+      <c r="D120">
+        <v>2</v>
+      </c>
+      <c r="G120">
+        <v>24</v>
+      </c>
+      <c r="H120">
+        <v>3</v>
+      </c>
+      <c r="I120">
+        <v>6</v>
+      </c>
+      <c r="L120">
+        <v>4</v>
+      </c>
+      <c r="U120">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="121" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A121" t="s">
+        <v>30</v>
+      </c>
+      <c r="B121">
+        <v>80</v>
+      </c>
+      <c r="G121">
+        <v>2</v>
+      </c>
+      <c r="I121">
+        <v>13</v>
+      </c>
+      <c r="J121">
+        <v>1</v>
+      </c>
+      <c r="N121">
+        <v>1</v>
+      </c>
+      <c r="R121">
+        <v>4</v>
+      </c>
+      <c r="U121">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="122" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A122" t="s">
+        <v>213</v>
+      </c>
+      <c r="B122">
+        <v>40</v>
+      </c>
+      <c r="G122">
+        <v>8</v>
+      </c>
+      <c r="I122">
+        <v>10</v>
+      </c>
+      <c r="J122">
+        <v>1</v>
+      </c>
+      <c r="N122">
+        <v>1</v>
+      </c>
+      <c r="R122">
+        <v>3</v>
+      </c>
+      <c r="U122">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="123" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A123" t="s">
+        <v>34</v>
+      </c>
+      <c r="B123">
+        <v>78</v>
+      </c>
+      <c r="G123">
+        <v>30</v>
+      </c>
+      <c r="I123">
+        <v>17</v>
+      </c>
+      <c r="N123">
+        <v>2</v>
+      </c>
+      <c r="R123">
+        <v>4</v>
+      </c>
+      <c r="U123">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="124" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A124" t="s">
+        <v>214</v>
+      </c>
+      <c r="B124">
+        <v>2</v>
+      </c>
+      <c r="U124">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="125" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A125" t="s">
+        <v>215</v>
+      </c>
+      <c r="B125">
+        <v>14</v>
+      </c>
+      <c r="H125">
+        <v>1</v>
+      </c>
+      <c r="I125">
+        <v>4</v>
+      </c>
+      <c r="U125">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A126" t="s">
+        <v>174</v>
+      </c>
+      <c r="B126">
+        <v>80</v>
+      </c>
+      <c r="G126">
+        <v>16</v>
+      </c>
+      <c r="I126">
+        <v>12</v>
+      </c>
+      <c r="J126">
+        <v>1</v>
+      </c>
+      <c r="R126">
+        <v>4</v>
+      </c>
+      <c r="U126">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="127" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A127" t="s">
+        <v>35</v>
+      </c>
+      <c r="B127">
+        <v>40</v>
+      </c>
+      <c r="G127">
+        <v>16</v>
+      </c>
+      <c r="I127">
+        <v>11</v>
+      </c>
+      <c r="J127">
+        <v>3</v>
+      </c>
+      <c r="R127">
+        <v>1</v>
+      </c>
+      <c r="U127">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="128" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A128" t="s">
+        <v>36</v>
+      </c>
+      <c r="B128">
+        <v>66</v>
+      </c>
+      <c r="G128">
+        <v>12</v>
+      </c>
+      <c r="H128">
+        <v>1</v>
+      </c>
+      <c r="I128">
+        <v>8</v>
+      </c>
+      <c r="N128">
+        <v>1</v>
+      </c>
+      <c r="R128">
+        <v>4</v>
+      </c>
+      <c r="U128">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="129" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A129" t="s">
+        <v>37</v>
+      </c>
+      <c r="B129">
+        <v>46</v>
+      </c>
+      <c r="H129">
+        <v>1</v>
+      </c>
+      <c r="I129">
+        <v>3</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
+      </c>
+      <c r="R129">
+        <v>4</v>
+      </c>
+      <c r="U129">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A130" t="s">
+        <v>201</v>
+      </c>
+      <c r="B130">
+        <v>27</v>
+      </c>
+      <c r="G130">
+        <v>3</v>
+      </c>
+      <c r="H130">
+        <v>1</v>
+      </c>
+      <c r="I130">
+        <v>5</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="S130">
+        <v>1</v>
+      </c>
+      <c r="U130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A131" t="s">
+        <v>38</v>
+      </c>
+      <c r="B131">
+        <v>65</v>
+      </c>
+      <c r="G131">
+        <v>4</v>
+      </c>
+      <c r="I131">
+        <v>9</v>
+      </c>
+      <c r="P131">
+        <v>1</v>
+      </c>
+      <c r="R131">
+        <v>4</v>
+      </c>
+      <c r="U131">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="132" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A132" t="s">
+        <v>39</v>
+      </c>
+      <c r="B132">
+        <v>15</v>
+      </c>
+      <c r="I132">
+        <v>6</v>
+      </c>
+      <c r="U132">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="133" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A133" t="s">
+        <v>40</v>
+      </c>
+      <c r="B133">
+        <v>46</v>
+      </c>
+      <c r="G133">
+        <v>4</v>
+      </c>
+      <c r="H133">
+        <v>1</v>
+      </c>
+      <c r="I133">
+        <v>8</v>
+      </c>
+      <c r="N133">
+        <v>2</v>
+      </c>
+      <c r="R133">
+        <v>4</v>
+      </c>
+      <c r="U133">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="134" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A134" t="s">
+        <v>41</v>
+      </c>
+      <c r="B134">
+        <v>34</v>
+      </c>
+      <c r="G134">
+        <v>4</v>
+      </c>
+      <c r="I134">
+        <v>12</v>
+      </c>
+      <c r="U134">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="137" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A137" s="1" t="s">
+        <v>111</v>
+      </c>
+      <c r="B137" t="s">
+        <v>1</v>
+      </c>
+      <c r="C137" t="s">
+        <v>2</v>
+      </c>
+      <c r="D137" t="s">
+        <v>3</v>
+      </c>
+      <c r="E137" t="s">
+        <v>4</v>
+      </c>
+      <c r="F137" t="s">
+        <v>5</v>
+      </c>
+      <c r="G137" t="s">
+        <v>6</v>
+      </c>
+      <c r="H137" t="s">
+        <v>7</v>
+      </c>
+      <c r="I137" t="s">
+        <v>8</v>
+      </c>
+      <c r="J137" t="s">
+        <v>9</v>
+      </c>
+      <c r="K137" t="s">
+        <v>10</v>
+      </c>
+      <c r="L137" t="s">
+        <v>11</v>
+      </c>
+      <c r="M137" t="s">
+        <v>12</v>
+      </c>
+      <c r="N137" t="s">
+        <v>13</v>
+      </c>
+      <c r="O137" t="s">
+        <v>14</v>
+      </c>
+      <c r="P137" t="s">
+        <v>15</v>
+      </c>
+      <c r="Q137" t="s">
+        <v>16</v>
+      </c>
+      <c r="R137" t="s">
+        <v>17</v>
+      </c>
+      <c r="S137" t="s">
+        <v>18</v>
+      </c>
+      <c r="T137" t="s">
+        <v>19</v>
+      </c>
+      <c r="U137" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="138" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A138" t="s">
+        <v>203</v>
+      </c>
+      <c r="B138">
+        <v>54</v>
+      </c>
+      <c r="D138">
+        <v>1</v>
+      </c>
+      <c r="G138">
+        <v>25</v>
+      </c>
+      <c r="I138">
+        <v>1</v>
+      </c>
+      <c r="J138">
+        <v>1</v>
+      </c>
+      <c r="U138">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="139" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A139" t="s">
+        <v>113</v>
+      </c>
+      <c r="B139">
+        <v>80</v>
+      </c>
+      <c r="C139">
+        <v>1</v>
+      </c>
+      <c r="G139">
+        <v>59</v>
+      </c>
+      <c r="H139">
+        <v>4</v>
+      </c>
+      <c r="I139">
+        <v>8</v>
+      </c>
+      <c r="N139">
+        <v>1</v>
+      </c>
+      <c r="U139">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="140" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A140" t="s">
+        <v>204</v>
+      </c>
+      <c r="B140">
+        <v>80</v>
+      </c>
+      <c r="C140">
+        <v>1</v>
+      </c>
+      <c r="G140">
+        <v>31</v>
+      </c>
+      <c r="I140">
+        <v>7</v>
+      </c>
+      <c r="J140">
+        <v>1</v>
+      </c>
+      <c r="U140">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="141" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A141" t="s">
+        <v>114</v>
+      </c>
+      <c r="B141">
+        <v>80</v>
+      </c>
+      <c r="C141">
+        <v>1</v>
+      </c>
+      <c r="G141">
+        <v>22</v>
+      </c>
+      <c r="H141">
+        <v>1</v>
+      </c>
+      <c r="I141">
+        <v>5</v>
+      </c>
+      <c r="J141">
+        <v>1</v>
+      </c>
+      <c r="N141">
+        <v>1</v>
+      </c>
+      <c r="U141">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="142" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A142" t="s">
+        <v>205</v>
+      </c>
+      <c r="B142">
+        <v>80</v>
+      </c>
+      <c r="G142">
+        <v>9</v>
+      </c>
+      <c r="H142">
+        <v>1</v>
+      </c>
+      <c r="I142">
+        <v>12</v>
+      </c>
+      <c r="U142">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="143" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A143" t="s">
+        <v>118</v>
+      </c>
+      <c r="B143">
+        <v>26</v>
+      </c>
+      <c r="C143">
+        <v>1</v>
+      </c>
+      <c r="E143">
+        <v>2</v>
+      </c>
+      <c r="G143">
+        <v>29</v>
+      </c>
+      <c r="H143">
+        <v>2</v>
+      </c>
+      <c r="I143">
+        <v>1</v>
+      </c>
+      <c r="U143">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="144" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A144" t="s">
+        <v>167</v>
+      </c>
+      <c r="B144">
+        <v>80</v>
+      </c>
+      <c r="E144">
+        <v>2</v>
+      </c>
+      <c r="F144">
+        <v>1</v>
+      </c>
+      <c r="G144">
+        <v>24</v>
+      </c>
+      <c r="H144">
+        <v>1</v>
+      </c>
+      <c r="I144">
+        <v>10</v>
+      </c>
+      <c r="L144">
+        <v>2</v>
+      </c>
+      <c r="N144">
+        <v>1</v>
+      </c>
+      <c r="U144">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="145" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A145" t="s">
+        <v>120</v>
+      </c>
+      <c r="B145">
+        <v>51</v>
+      </c>
+      <c r="G145">
+        <v>2</v>
+      </c>
+      <c r="I145">
+        <v>4</v>
+      </c>
+      <c r="J145">
+        <v>1</v>
+      </c>
+      <c r="L145">
+        <v>2</v>
+      </c>
+      <c r="U145">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="146" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A146" t="s">
+        <v>177</v>
+      </c>
+      <c r="B146">
+        <v>29</v>
+      </c>
+      <c r="D146">
+        <v>2</v>
+      </c>
+      <c r="G146">
+        <v>6</v>
+      </c>
+      <c r="J146">
+        <v>1</v>
+      </c>
+      <c r="L146">
+        <v>1</v>
+      </c>
+      <c r="U146">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="147" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A147" t="s">
+        <v>206</v>
+      </c>
+      <c r="B147">
+        <v>5</v>
+      </c>
+      <c r="G147">
+        <v>20</v>
+      </c>
+      <c r="I147">
+        <v>2</v>
+      </c>
+      <c r="U147">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="148" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A148" t="s">
+        <v>122</v>
+      </c>
+      <c r="B148">
+        <v>65</v>
+      </c>
+      <c r="G148">
+        <v>38</v>
+      </c>
+      <c r="H148">
+        <v>1</v>
+      </c>
+      <c r="I148">
+        <v>6</v>
+      </c>
+      <c r="R148">
+        <v>2</v>
+      </c>
+      <c r="U148">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="149" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A149" t="s">
+        <v>123</v>
+      </c>
+      <c r="B149">
+        <v>62</v>
+      </c>
+      <c r="I149">
+        <v>11</v>
+      </c>
+      <c r="J149">
+        <v>1</v>
+      </c>
+      <c r="N149">
+        <v>1</v>
+      </c>
+      <c r="R149">
+        <v>1</v>
+      </c>
+      <c r="U149">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="150" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A150" t="s">
+        <v>124</v>
+      </c>
+      <c r="B150">
+        <v>28</v>
+      </c>
+      <c r="G150">
+        <v>7</v>
+      </c>
+      <c r="H150">
+        <v>1</v>
+      </c>
+      <c r="I150">
+        <v>4</v>
+      </c>
+      <c r="R150">
+        <v>2</v>
+      </c>
+      <c r="U150">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="151" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A151" t="s">
+        <v>125</v>
+      </c>
+      <c r="B151">
+        <v>18</v>
+      </c>
+      <c r="G151">
+        <v>3</v>
+      </c>
+      <c r="I151">
+        <v>4</v>
+      </c>
+      <c r="R151">
+        <v>1</v>
+      </c>
+      <c r="U151">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="152" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A152" t="s">
+        <v>126</v>
+      </c>
+      <c r="B152">
+        <v>80</v>
+      </c>
+      <c r="C152">
+        <v>2</v>
+      </c>
+      <c r="D152">
+        <v>1</v>
+      </c>
+      <c r="G152">
+        <v>82</v>
+      </c>
+      <c r="H152">
+        <v>2</v>
+      </c>
+      <c r="I152">
+        <v>5</v>
+      </c>
+      <c r="R152">
+        <v>2</v>
+      </c>
+      <c r="U152">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="153" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A153" t="s">
+        <v>127</v>
+      </c>
+      <c r="B153">
+        <v>54</v>
+      </c>
+      <c r="C153">
+        <v>1</v>
+      </c>
+      <c r="G153">
+        <v>8</v>
+      </c>
+      <c r="I153">
+        <v>10</v>
+      </c>
+      <c r="J153">
+        <v>1</v>
+      </c>
+      <c r="U153">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="154" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A154" t="s">
+        <v>128</v>
+      </c>
+      <c r="B154">
+        <v>80</v>
+      </c>
+      <c r="G154">
+        <v>12</v>
+      </c>
+      <c r="I154">
+        <v>15</v>
+      </c>
+      <c r="J154">
+        <v>1</v>
+      </c>
+      <c r="N154">
+        <v>1</v>
+      </c>
+      <c r="P154">
+        <v>2</v>
+      </c>
+      <c r="R154">
+        <v>2</v>
+      </c>
+      <c r="U154">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="155" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A155" t="s">
+        <v>129</v>
+      </c>
+      <c r="B155">
+        <v>5</v>
+      </c>
+      <c r="G155">
+        <v>1</v>
+      </c>
+      <c r="I155">
+        <v>1</v>
+      </c>
+      <c r="U155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A156" t="s">
+        <v>130</v>
+      </c>
+      <c r="B156">
+        <v>64</v>
+      </c>
+      <c r="G156">
+        <v>28</v>
+      </c>
+      <c r="H156">
+        <v>5</v>
+      </c>
+      <c r="I156">
+        <v>10</v>
+      </c>
+      <c r="J156">
+        <v>1</v>
+      </c>
+      <c r="N156">
+        <v>1</v>
+      </c>
+      <c r="R156">
+        <v>2</v>
+      </c>
+      <c r="S156">
+        <v>1</v>
+      </c>
+      <c r="U156">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="157" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A157" t="s">
+        <v>131</v>
+      </c>
+      <c r="B157">
+        <v>75</v>
+      </c>
+      <c r="I157">
+        <v>10</v>
+      </c>
+      <c r="J157">
+        <v>1</v>
+      </c>
+      <c r="R157">
+        <v>2</v>
+      </c>
+      <c r="U157">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="158" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A158" t="s">
+        <v>132</v>
+      </c>
+      <c r="B158">
+        <v>13</v>
+      </c>
+      <c r="G158">
+        <v>3</v>
+      </c>
+      <c r="H158">
+        <v>1</v>
+      </c>
+      <c r="I158">
+        <v>6</v>
+      </c>
+      <c r="J158">
+        <v>1</v>
+      </c>
+      <c r="N158">
+        <v>1</v>
+      </c>
+      <c r="U158">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="159" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A159" t="s">
+        <v>133</v>
+      </c>
+      <c r="B159">
+        <v>29</v>
+      </c>
+      <c r="G159">
+        <v>10</v>
+      </c>
+      <c r="I159">
+        <v>6</v>
+      </c>
+      <c r="R159">
+        <v>2</v>
+      </c>
+      <c r="U159">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="160" spans="1:21" x14ac:dyDescent="0.2">
+      <c r="A160" t="s">
+        <v>134</v>
+      </c>
+      <c r="B160">
+        <v>51</v>
+      </c>
+      <c r="G160">
+        <v>2</v>
+      </c>
+      <c r="H160">
+        <v>1</v>
+      </c>
+      <c r="I160">
+        <v>5</v>
+      </c>
+      <c r="U160">
+        <v>7</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>